--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$203</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>66 / 111 / 26</t>
+          <t>65 / 111 / 26</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 42</t>
+          <t>остаток 80</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>остаток 80</t>
+          <t>остаток 46</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>остаток 46</t>
+          <t>остаток 149</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>остаток 149</t>
+          <t>остаток 104</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>остаток 104</t>
+          <t>остаток 42</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>остаток 42</t>
+          <t>остаток 76</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>остаток 76</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 47</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>остаток 47</t>
+          <t>остаток 30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>остаток 30</t>
+          <t>остаток 40</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>остаток 40</t>
+          <t>остаток 5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>остаток 5</t>
+          <t>остаток 28</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>остаток 28</t>
+          <t>остаток 8</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>остаток 8</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>остаток 17</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>остаток 17</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>остаток 12</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>остаток 12</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>остаток 30</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>остаток 30</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>остаток 30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>остаток 30</t>
+          <t>остаток 104</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>остаток 104</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>остаток 35</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>остаток 35</t>
+          <t>остаток 130</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>остаток 130</t>
+          <t>остаток 52</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>остаток 52</t>
+          <t>остаток 53</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>остаток 53</t>
+          <t>остаток 20</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>остаток 20</t>
+          <t>остаток 30</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>остаток 30</t>
+          <t>остаток 23</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>остаток 23</t>
+          <t>остаток 75</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2330,27 +2330,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>остаток 75</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2867,34 +2867,34 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 50 ≠ мастер 0</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -2938,27 +2938,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2970,27 +2970,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>WB: «Болт мехатроника DSG7 DQ200 0AM 0CW Короткий» ≠ мастер: «Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X30»</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>update-cards</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>WB: «Болт мехатроника DSG7 DQ200 0AM 0CW Короткий» ≠ мастер: «Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X30»</t>
+          <t>WB: «Фильтр мехатроника DQ250 02E DSG6» ≠ мастер: «Фильтр мехатроника DSG6 DQ250 02E305051C»</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>WB: «Фильтр мехатроника DQ250 02E DSG6» ≠ мастер: «Фильтр мехатроника DSG6 DQ250 02E305051C»</t>
+          <t>WB: «Корпус фильтра DSG6 DQ250 02E305045» ≠ мастер: «Корпус масляного фильтра мехатроника DSG6 DQ250 02»</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>WB: «Корпус фильтра DSG6 DQ250 02E305045» ≠ мастер: «Корпус масляного фильтра мехатроника DSG6 DQ250 02»</t>
+          <t>WB: «Заглушка корпуса КПП DSG7 DQ200 0AM 0CW» ≠ мастер: «Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301»</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>WB: «Заглушка корпуса КПП DSG7 DQ200 0AM 0CW» ≠ мастер: «Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301»</t>
+          <t>WB: «Транспортная заглушка мехатроника DSG7 DQ200 0AM 0» ≠ мастер: «Транспортная заглушка мехатроника DSG7 DQ200 0AM32»</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>WB: «Транспортная заглушка мехатроника DSG7 DQ200 0AM 0» ≠ мастер: «Транспортная заглушка мехатроника DSG7 DQ200 0AM32»</t>
+          <t>WB: «Крышка мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM»</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>WB: «Крышка мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM»</t>
+          <t>WB: «Сальник толкателя вилки мехатроника DSG7 DQ200 0AM» ≠ мастер: «Сальник толкателя вилки мехатроника DSG7 DQ200 0AM»</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>WB: «Сальник толкателя вилки мехатроника DSG7 DQ200 0AM» ≠ мастер: «Сальник толкателя вилки мехатроника DSG7 DQ200 0AM»</t>
+          <t>WB: «Улучшенный фильтр мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Фильтр мехатроника DSG7 DQ200 0AM325433E»</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>WB: «Улучшенный фильтр мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Фильтр мехатроника DSG7 DQ200 0AM325433E»</t>
+          <t>WB: «Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>WB: «Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+          <t>WB: «Гидроаккумулятор DSG7 DQ200 0AM 0CW» ≠ мастер: «Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал 0»</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>WB: «Гидроаккумулятор DSG7 DQ200 0AM 0CW» ≠ мастер: «Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал 0»</t>
+          <t>WB: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «Корпус фильтра мехатроника DSG7 DQ500 0BH325183B»</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>WB: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «Корпус фильтра мехатроника DSG7 DQ500 0BH325183B»</t>
+          <t>WB: «Корпус фильтра DQ500 DSG7 0BH325183 B (красный)» ≠ мастер: «Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, »</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>WB: «Корпус фильтра DQ500 DSG7 0BH325183 B (красный)» ≠ мастер: «Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, »</t>
+          <t>WB: «Ремкомплект мехатроника DSG 7 DQ200 Плита сальники» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 гидроплита 0AM3»</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>WB: «Ремкомплект мехатроника DSG 7 DQ200 Плита сальники» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 гидроплита 0AM3»</t>
+          <t>WB: «Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Втулка (гильза) штока мехатроника DSG7 DQ200 0AM32»</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>WB: «Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Втулка (гильза) штока мехатроника DSG7 DQ200 0AM32»</t>
+          <t>WB: «Ремкомплект штоков DSG7 DQ200 2 пыльника 2 сальник» ≠ мастер: «Ремкомплект 2 штоков мехатроника DSG7 DQ200 пыльни»</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>WB: «Ремкомплект штоков DSG7 DQ200 2 пыльника 2 сальник» ≠ мастер: «Ремкомплект 2 штоков мехатроника DSG7 DQ200 пыльни»</t>
+          <t>WB: «Мехатроник DSG7 DQ200 0AM 0CW» ≠ мастер: «Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО»</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>WB: «Мехатроник DSG7 DQ200 0AM 0CW» ≠ мастер: «Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО»</t>
+          <t>WB: «Мехатроник DQ200 DSG7 0AM 0CW с Эл. платой» ≠ мастер: «Мехатроник DSG7 DQ200 в сборе с электронной 0AM927»</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>WB: «Мехатроник DQ200 DSG7 0AM 0CW с Эл. платой» ≠ мастер: «Мехатроник DSG7 DQ200 в сборе с электронной 0AM927»</t>
+          <t>WB: «Крышка мехатроника DSG7 + прокладка поддона dq200 » ≠ мастер: «усиленная прокладка мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>WB: «Крышка мехатроника DSG7 + прокладка поддона dq200 » ≠ мастер: «усиленная прокладка мехатроника DSG7 DQ200»</t>
+          <t>WB: «Болты мехатроника DSG 7 DQ200 (0AM/0CW) комплект 7» ≠ мастер: «Комплект болтов мехатроника DSG7 DQ200, 7 шт»</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>WB: «Болты мехатроника DSG 7 DQ200 (0AM/0CW) комплект 7» ≠ мастер: «Комплект болтов мехатроника DSG7 DQ200, 7 шт»</t>
+          <t>WB: «Комплект штока мехатроника DSG7 DQ200 сальник пыль» ≠ мастер: «Ремкомплект штока мехатроника DSG7 DQ200 сальник п»</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>WB: «Комплект штока мехатроника DSG7 DQ200 сальник пыль» ≠ мастер: «Ремкомплект штока мехатроника DSG7 DQ200 сальник п»</t>
+          <t>WB: «Оригинал VAG пластины мехатроиника dsg7 dq200» ≠ мастер: «пластины на соленоиды мехатроника DSG7 DQ200, ориг»</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>WB: «Оригинал VAG пластины мехатроиника dsg7 dq200» ≠ мастер: «пластины на соленоиды мехатроника DSG7 DQ200, ориг»</t>
+          <t>WB: «Поршень вилки мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Поршень (толкатель) вилки мехатроника DSG7 DQ200 0»</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>WB: «Поршень вилки мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Поршень (толкатель) вилки мехатроника DSG7 DQ200 0»</t>
+          <t>WB: «Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM» ≠ мастер: «Ремкомплект прокладок мехатроника DSG7 DQ200 0AM32»</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>WB: «Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM» ≠ мастер: «Ремкомплект прокладок мехатроника DSG7 DQ200 0AM32»</t>
+          <t>WB: «Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт» ≠ мастер: «Соленоид переключения Shift DSG7 DQ200 0AM325025N»</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>WB: «Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт» ≠ мастер: «Соленоид переключения Shift DSG7 DQ200 0AM325025N»</t>
+          <t>WB: «Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт» ≠ мастер: «Крышка штока мехатроника DSG7 DQ200 0AM325025Q»</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>WB: «Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт» ≠ мастер: «Крышка штока мехатроника DSG7 DQ200 0AM325025Q»</t>
+          <t>WB: «Усиленное опорное кольцо толкателя DSG7 DQ200 0AM» ≠ мастер: «Усиленное опорное кольцо толкателя DSG7 DQ200 0AM3»</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>WB: «Усиленное опорное кольцо толкателя DSG7 DQ200 0AM» ≠ мастер: «Усиленное опорное кольцо толкателя DSG7 DQ200 0AM3»</t>
+          <t>WB: «Длинный шток 0AM325091E 101 мм+втулка мехатроника » ≠ мастер: «Ремкомплект Усиленный длинный шток 0AM325091E + DS»</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>WB: «Длинный шток 0AM325091E 101 мм+втулка мехатроника » ≠ мастер: «Ремкомплект Усиленный длинный шток 0AM325091E + DS»</t>
+          <t>WB: «Короткий шток 0AM325091F 99 мм+втулка мехатроника » ≠ мастер: «Ремкомплект Усиленный короткий шток 0AM325091F + D»</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>WB: «Короткий шток 0AM325091F 99 мм+втулка мехатроника » ≠ мастер: «Ремкомплект Усиленный короткий шток 0AM325091F + D»</t>
+          <t>WB: «Поршень штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Усиленный поршень штока мехатроника DSG7 DQ200 0AM»</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>WB: «Поршень штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Усиленный поршень штока мехатроника DSG7 DQ200 0AM»</t>
+          <t>WB: «Сальник манжет штока сцепления мехатроник DSG7 DQ2» ≠ мастер: «Сальник-манжета штока сцепления DSG7 DQ200 0AM3250»</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>WB: «Сальник манжет штока сцепления мехатроник DSG7 DQ2» ≠ мастер: «Сальник-манжета штока сцепления DSG7 DQ200 0AM3250»</t>
+          <t>WB: «Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW» ≠ мастер: «Усиленная гидроплита мехатроника DSG7 DQ200 0AM325»</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW» ≠ мастер: «Усиленная гидроплита мехатроника DSG7 DQ200 0AM325»</t>
+          <t>WB: «Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0A» ≠ мастер: «Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325»</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>WB: «Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0A» ≠ мастер: «Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325»</t>
+          <t>WB: «Шток мехатроника DSG 7 DQ200 0am325091f 99 мм коро» ≠ мастер: «Усиленный шток мехатроника DSG7 DQ200 99мм 0AM3250»</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>WB: «Шток мехатроника DSG 7 DQ200 0am325091f 99 мм коро» ≠ мастер: «Усиленный шток мехатроника DSG7 DQ200 99мм 0AM3250»</t>
+          <t>WB: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW п»</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>WB: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW п»</t>
+          <t>WB: «Пыльник штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Пыльник штока мехатроника DSG7 DQ200 122390AK-AF»</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>WB: «Пыльник штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Пыльник штока мехатроника DSG7 DQ200 122390AK-AF»</t>
+          <t>WB: «Пыльник штока DQ200 DSG7 0AM Оригинал Volkswagen Г» ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>WB: «Пыльник штока DQ200 DSG7 0AM Оригинал Volkswagen Г» ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+          <t>WB: «Фильтр-сетка соленоидов N436 / N440 DSG7 0B5 DL501» ≠ мастер: «Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B»</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>WB: «Фильтр-сетка соленоидов N436 / N440 DSG7 0B5 DL501» ≠ мастер: «Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B»</t>
+          <t>WB: «Гидроблок JF011E Новое поколение Nissan Mitsubishi» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>WB: «Гидроблок JF011E Новое поколение Nissan Mitsubishi» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+          <t>WB: «Гидроблок JF015E 1.6 Л RE0F11A Nissan, Renault, Mi» ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>WB: «Гидроблок JF015E 1.6 Л RE0F11A Nissan, Renault, Mi» ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+          <t>WB: «Гидроблок JF015E 1.8 Л RE0F11A Nissan Renault Mits» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>WB: «Гидроблок JF015E 1.8 Л RE0F11A Nissan Renault Mits» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4292,17 +4292,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>WB: «Болт мехатроника DSG7 DQ200 0AM 0CW Длинный» ≠ мастер: «Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001»</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>update-cards</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>WB: «Болт мехатроника DSG7 DQ200 0AM 0CW Длинный» ≠ мастер: «Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001»</t>
+          <t>WB: «Усиленная плита + улучшенный фильтр мехатроника DS» ≠ мастер: «улучшенный фильтр мехатроника DSG7 DQ200, комплект»</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>WB: «Усиленная плита + улучшенный фильтр мехатроника DS» ≠ мастер: «улучшенный фильтр мехатроника DSG7 DQ200, комплект»</t>
+          <t>WB: «Плита + фильтр + 2 пыльника + 2 сальника ориг VAG » ≠ мастер: «Плита + 2 сальника ориг VAG DSG7 DQ200, полный ком»</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>WB: «Плита + фильтр + 2 пыльника + 2 сальника ориг VAG » ≠ мастер: «Плита + 2 сальника ориг VAG DSG7 DQ200, полный ком»</t>
+          <t>WB: «Усиленная гидроплита + 2 пыльника + 2 сальника DSG» ≠ мастер: «2 пыльника + 2 сальника DSG7 DQ200, комплект без ф»</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита + 2 пыльника + 2 сальника DSG» ≠ мастер: «2 пыльника + 2 сальника DSG7 DQ200, комплект без ф»</t>
+          <t>WB: «Сепараторная пластина + пластины на соленоиды меха» ≠ мастер: «пластины на соленоиды мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4442,27 +4442,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>WB: «Сепараторная пластина + пластины на соленоиды меха» ≠ мастер: «пластины на соленоиды мехатроника DSG7 DQ200»</t>
+          <t>на Авито 890 ≠ в нашем файле 500</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4484,17 +4484,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 500</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4548,17 +4548,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 1450 ≠ в нашем файле 2980</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2980</t>
+          <t>на Авито 850 ≠ в нашем файле 1490</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1490</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>id 4125224328 статус active</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>id 3965227267 статус rejected</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6138,27 +6138,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет цены без комиссии</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>на Авито цена как на маркетплейсах (7500); по правилу ≈ 3750</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>добавить plita-filtr-v2 = 3750 в data/avito_site_price_overrides.xlsx</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>на Авито цена как на маркетплейсах (7500); по правилу ≈ 3750</t>
+          <t>на Авито цена как на маркетплейсах (3990); по правилу ≈ 1995</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>добавить plita-filtr-v2 = 3750 в data/avito_site_price_overrides.xlsx</t>
+          <t>добавить porshni-usil-pylniki-kryshki-v2 = 1995 в data/avito_site_price_overrides.xlsx</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>на Авито цена как на маркетплейсах (3990); по правилу ≈ 1995</t>
+          <t>на Авито цена как на маркетплейсах (2980); по правилу ≈ 1490</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>добавить porshni-usil-pylniki-kryshki-v2 = 1995 в data/avito_site_price_overrides.xlsx</t>
+          <t>добавить pylniki-shtokov-orig-v2 = 1490 в data/avito_site_price_overrides.xlsx</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>на Авито цена как на маркетплейсах (2980); по правилу ≈ 1490</t>
+          <t>на Авито цена как на маркетплейсах (1490); по правилу ≈ 745</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>добавить pylniki-shtokov-orig-v2 = 1490 в data/avito_site_price_overrides.xlsx</t>
+          <t>добавить salnik-shtoka-orig-v2 = 745 в data/avito_site_price_overrides.xlsx</t>
         </is>
       </c>
     </row>
@@ -6266,27 +6266,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>0am325025Y</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>нет цены без комиссии</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>на Авито цена как на маркетплейсах (1490); по правилу ≈ 745</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>добавить salnik-shtoka-orig-v2 = 745 в data/avito_site_price_overrides.xlsx</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>0am325025e</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6372,17 +6372,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>jf015</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6404,49 +6404,49 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jf015</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6554,27 +6554,27 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>цена не равна половине</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Авито/сайт 745, половина маркетплейса 1175</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Авито/сайт 745, половина маркетплейса 1175</t>
+          <t>Авито/сайт 925, половина маркетплейса 1490</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6618,27 +6618,27 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>цена не равна половине</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Авито/сайт 925, половина маркетплейса 1490</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>оставить, если это сознательная цена</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>31705-1XF1A</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
+          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7250,40 +7250,8 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>gidroakkumulyator-orig</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F204"/>
+  <autoFilter ref="A1:F203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9772,9 +9740,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>65 / 111 / 26</t>
+          <t>26 / 77 / 26</t>
         </is>
       </c>
     </row>
@@ -545,41 +545,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>Маркет: название</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WB: название</t>
+          <t>Авито: ошибка автозагрузки</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Маркет: название</t>
+          <t>WB: название</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Авито: ошибка автозагрузки</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:F130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>остаток 1</t>
+          <t>WB 4160 ≠ мастер 1990</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>остаток 177</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WB 4160 ≠ мастер 1990</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>остаток 2</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>остаток 75</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>остаток 75</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>остаток 56</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 80</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>остаток 46</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1082,27 +1082,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>остаток 149</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1114,27 +1114,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>остаток 104</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1146,27 +1146,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>остаток 42</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1178,27 +1178,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>остаток 76</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1210,27 +1210,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>остаток 47</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1338,27 +1338,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>остаток 30</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1370,27 +1370,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>остаток 40</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>остаток 5</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1434,27 +1434,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>остаток 28</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1466,27 +1466,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>остаток 8</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1498,27 +1498,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>остаток 8</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1530,27 +1530,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>остаток 8</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1562,27 +1562,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>остаток 8</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1594,743 +1594,743 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>остаток</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ozon 50 ≠ мастер 0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>push-stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tilda</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0AM927769D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>WB: «Прокладки электронной платы DSG7 DQ200 0AM927769N» ≠ мастер: «Электронная плата мехатроника DSG7 DQ200 0AM927769»</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>WB: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254» ≠ мастер: «Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW п»</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>WB: «Прокладки + сальники + пыльники DSG7 DQ200, Герман» ≠ мастер: «пыльники мехатроника DSG7 DQ200, оригинал Германия»</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TESTWB001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-orig</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>WB: «Оригинальные пластины на соленоиды VAG DSG7 DQ200» ≠ мастер: «Оригинальные пластины на соленоиды VAG DSG7 DQ200 »</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WB: «Усиленная гидроплита + фильтр DSG7 DQ200, комплект» ≠ мастер: «фильтр мехатроника DSG7 DQ200, комплект»</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WB: «Усиленная гидроплита + фильтр + 2 пыльника штоков » ≠ мастер: «фильтр + 2 пыльника штоков DSG7 DQ200, комплект»</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WB: «Усиленная плита + фильтр + 2 пыльника DSG7 DQ200, » ≠ мастер: «фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, к»</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>WB: «Усиленная гидроплита + фильтр + 2 пыльника DQ200» ≠ мастер: «фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полны»</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>остаток 8</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>WB: «Усиленная плита + фильтр + 2 сальника DSG7 DQ200, » ≠ мастер: «фильтр + 2 оригинальных сальника VAG DSG7 DQ200, к»</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>остаток 45</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>WB: «Комплект 4 толкателей вилок + 4 сальника DSG7 DQ20» ≠ мастер: «4 сальника DSG7 DQ200, на весь мехатроник»</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>остаток 17</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>остаток 31</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>остаток 12</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>остаток 100</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>остаток 30</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>WB: «Толкатели вилок + сальники + усиленные DSG7 DQ200» ≠ мастер: «усиленные алюминиевые сальники DSG7 DQ200, комплек»</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>update-cards</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>55565480</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>на Авито 890 ≠ в нашем файле 500</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>id 4444617509 статус active</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>id 3964915138 статус old</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>остаток 43</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>remkomplekt-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>остаток 30</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>остаток 104</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>на Авито 1450 ≠ в нашем файле 2980</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>остаток 50</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>salnik-tolkatelya-alum</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>остаток 35</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>остаток 130</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>остаток 52</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>salniki-tolkatelya-4sht</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>остаток 53</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>salnikprivod-l</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>остаток 20</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>salnikprivod-r</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>остаток 20</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>остаток 20</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>остаток 20</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>stalnaya-vstavka-plity</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>остаток 30</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>tolkateli-4-salniki-4</t>
-        </is>
-      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>остаток 23</t>
+          <t>на Авито 850 ≠ в нашем файле 1490</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>остаток 23</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>остаток 75</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2340,29 +2340,29 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2372,29 +2372,29 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2404,29 +2404,29 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2436,29 +2436,29 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2468,29 +2468,29 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2500,29 +2500,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2532,29 +2532,29 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2564,29 +2564,29 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2596,29 +2596,29 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2628,29 +2628,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2660,29 +2660,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2692,29 +2692,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2724,29 +2724,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2756,29 +2756,29 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2788,29 +2788,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2820,29 +2820,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2874,27 +2874,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2906,27 +2906,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2938,27 +2938,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2970,27 +2970,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>WB: «Болт мехатроника DSG7 DQ200 0AM 0CW Короткий» ≠ мастер: «Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X30»</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3002,27 +3002,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>WB: «Фильтр мехатроника DQ250 02E DSG6» ≠ мастер: «Фильтр мехатроника DSG6 DQ250 02E305051C»</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3034,27 +3034,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>WB: «Корпус фильтра DSG6 DQ250 02E305045» ≠ мастер: «Корпус масляного фильтра мехатроника DSG6 DQ250 02»</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3066,27 +3066,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>WB: «Заглушка корпуса КПП DSG7 DQ200 0AM 0CW» ≠ мастер: «Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301»</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3098,27 +3098,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>WB: «Транспортная заглушка мехатроника DSG7 DQ200 0AM 0» ≠ мастер: «Транспортная заглушка мехатроника DSG7 DQ200 0AM32»</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3130,27 +3130,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>WB: «Крышка мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM»</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3162,27 +3162,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>WB: «Сальник толкателя вилки мехатроника DSG7 DQ200 0AM» ≠ мастер: «Сальник толкателя вилки мехатроника DSG7 DQ200 0AM»</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3194,27 +3194,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>WB: «Улучшенный фильтр мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Фильтр мехатроника DSG7 DQ200 0AM325433E»</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3226,27 +3226,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>WB: «Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3258,27 +3258,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>WB: «Гидроаккумулятор DSG7 DQ200 0AM 0CW» ≠ мастер: «Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал 0»</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3290,27 +3290,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>WB: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «Корпус фильтра мехатроника DSG7 DQ500 0BH325183B»</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3322,27 +3322,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>WB: «Корпус фильтра DQ500 DSG7 0BH325183 B (красный)» ≠ мастер: «Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, »</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3354,27 +3354,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>WB: «Ремкомплект мехатроника DSG 7 DQ200 Плита сальники» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 гидроплита 0AM3»</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3386,27 +3386,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>WB: «Втулка гильза штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Втулка (гильза) штока мехатроника DSG7 DQ200 0AM32»</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3418,27 +3418,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>WB: «Ремкомплект штоков DSG7 DQ200 2 пыльника 2 сальник» ≠ мастер: «Ремкомплект 2 штоков мехатроника DSG7 DQ200 пыльни»</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3450,27 +3450,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>WB: «Мехатроник DSG7 DQ200 0AM 0CW» ≠ мастер: «Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО»</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3482,27 +3482,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>WB: «Мехатроник DQ200 DSG7 0AM 0CW с Эл. платой» ≠ мастер: «Мехатроник DSG7 DQ200 в сборе с электронной 0AM927»</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3514,27 +3514,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>WB: «Крышка мехатроника DSG7 + прокладка поддона dq200 » ≠ мастер: «усиленная прокладка мехатроника DSG7 DQ200»</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3546,27 +3546,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>WB: «Болты мехатроника DSG 7 DQ200 (0AM/0CW) комплект 7» ≠ мастер: «Комплект болтов мехатроника DSG7 DQ200, 7 шт»</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3578,27 +3578,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>WB: «Комплект штока мехатроника DSG7 DQ200 сальник пыль» ≠ мастер: «Ремкомплект штока мехатроника DSG7 DQ200 сальник п»</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3610,27 +3610,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>WB: «Оригинал VAG пластины мехатроиника dsg7 dq200» ≠ мастер: «пластины на соленоиды мехатроника DSG7 DQ200, ориг»</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3642,27 +3642,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>WB: «Поршень вилки мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Поршень (толкатель) вилки мехатроника DSG7 DQ200 0»</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3674,27 +3674,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>WB: «Ремкомплект мехатроника (прокладки) DSG7 DQ200 0AM» ≠ мастер: «Ремкомплект прокладок мехатроника DSG7 DQ200 0AM32»</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3706,27 +3706,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>WB: «Соленоид DSG7 DQ200 0AM 0CW Shift 1 шт» ≠ мастер: «Соленоид переключения Shift DSG7 DQ200 0AM325025N»</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3738,27 +3738,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>WB: «Крышка штока мехатроника DSG7 DQ200 0AM 0CW 1шт» ≠ мастер: «Крышка штока мехатроника DSG7 DQ200 0AM325025Q»</t>
+          <t>id 4125224328 статус active</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3770,27 +3770,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>WB: «Усиленное опорное кольцо толкателя DSG7 DQ200 0AM» ≠ мастер: «Усиленное опорное кольцо толкателя DSG7 DQ200 0AM3»</t>
+          <t>id 3965227267 статус rejected</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3802,27 +3802,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>нет цены без комиссии</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>WB: «Длинный шток 0AM325091E 101 мм+втулка мехатроника » ≠ мастер: «Ремкомплект Усиленный длинный шток 0AM325091E + DS»</t>
+          <t>на Авито цена как на маркетплейсах (7500); по правилу ≈ 3750</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>добавить plita-filtr-v2 = 3750 в data/avito_site_price_overrides.xlsx</t>
         </is>
       </c>
     </row>
@@ -3834,27 +3834,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>нет цены без комиссии</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>WB: «Короткий шток 0AM325091F 99 мм+втулка мехатроника » ≠ мастер: «Ремкомплект Усиленный короткий шток 0AM325091F + D»</t>
+          <t>на Авито цена как на маркетплейсах (3990); по правилу ≈ 1995</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>добавить porshni-usil-pylniki-kryshki-v2 = 1995 в data/avito_site_price_overrides.xlsx</t>
         </is>
       </c>
     </row>
@@ -3866,27 +3866,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>нет цены без комиссии</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>WB: «Поршень штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Усиленный поршень штока мехатроника DSG7 DQ200 0AM»</t>
+          <t>на Авито цена как на маркетплейсах (2980); по правилу ≈ 1490</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>добавить pylniki-shtokov-orig-v2 = 1490 в data/avito_site_price_overrides.xlsx</t>
         </is>
       </c>
     </row>
@@ -3898,27 +3898,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>нет цены без комиссии</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>WB: «Сальник манжет штока сцепления мехатроник DSG7 DQ2» ≠ мастер: «Сальник-манжета штока сцепления DSG7 DQ200 0AM3250»</t>
+          <t>на Авито цена как на маркетплейсах (1490); по правилу ≈ 745</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>добавить salnik-shtoka-orig-v2 = 745 в data/avito_site_price_overrides.xlsx</t>
         </is>
       </c>
     </row>
@@ -3930,27 +3930,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325025Y</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW» ≠ мастер: «Усиленная гидроплита мехатроника DSG7 DQ200 0AM325»</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -3962,27 +3962,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325025e</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>WB: «Шток мехатроника DSG7 DQ200 0AM / 0CW (101 мм), 0A» ≠ мастер: «Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325»</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -3994,27 +3994,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>WB: «Шток мехатроника DSG 7 DQ200 0am325091f 99 мм коро» ≠ мастер: «Усиленный шток мехатроника DSG7 DQ200 99мм 0AM3250»</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -4026,27 +4026,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>WB: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW п»</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -4058,3200 +4058,864 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>jf015</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tilda</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Dq500</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Авито/сайт</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>цена не равна половине</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Авито/сайт 745, половина маркетплейса 1175</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>оставить, если это сознательная цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Авито/сайт</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>цена не равна половине</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Авито/сайт 925, половина маркетплейса 1490</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>оставить, если это сознательная цена</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0AM325467J</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>WB: «Пыльник штока мехатроника DSG7 DQ200 0AM 0CW» ≠ мастер: «Пыльник штока мехатроника DSG7 DQ200 122390AK-AF»</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0AM325473</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0am325025</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0cw0am</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0cw0am325025</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0cw0amdsgdq200</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0cw325025h</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>WB: «Пыльник штока DQ200 DSG7 0AM Оригинал Volkswagen Г» ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>123014‑AF</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>WB: «Фильтр-сетка соленоидов N436 / N440 DSG7 0B5 DL501» ≠ мастер: «Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF 0B»</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>31705-1XF1A</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>WB: «Гидроблок JF011E Новое поколение Nissan Mitsubishi» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
         <is>
           <t>31705-X428B</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>WB: «Гидроблок JF015E 1.6 Л RE0F11A Nissan, Renault, Mi» ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>WB: «Гидроблок JF015E 1.8 Л RE0F11A Nissan Renault Mits» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>TESTWB001</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>WHT001922</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>WB: «Болт мехатроника DSG7 DQ200 0AM 0CW Длинный» ≠ мастер: «Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001»</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>plita-filtr-orig</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>WB: «Усиленная плита + улучшенный фильтр мехатроника DS» ≠ мастер: «улучшенный фильтр мехатроника DSG7 DQ200, комплект»</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>EA888</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>WB: «Плита + фильтр + 2 пыльника + 2 сальника ориг VAG » ≠ мастер: «Плита + 2 сальника ориг VAG DSG7 DQ200, полный ком»</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>EA888gen3</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>WB: «Усиленная гидроплита + 2 пыльника + 2 сальника DSG» ≠ мастер: «2 пыльника + 2 сальника DSG7 DQ200, комплект без ф»</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ea888gen3</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>WB: «Сепараторная пластина + пластины на соленоиды меха» ≠ мастер: «пластины на соленоиды мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>update-cards</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>55565480</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>на Авито 890 ≠ в нашем файле 500</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>id 4444617509 статус active</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>id 3964915138 статус old</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig-v2</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>на Авито 1450 ≠ в нашем файле 2980</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>на Авито 850 ≠ в нашем файле 1490</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>id 4284998704 статус active</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>id 4284880578 статус active</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>id 4220734432 статус active</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>id 4125069388 статус active</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>id 4284610725 статус active</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>id 4285296851 статус active</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>id 4284955885 статус active</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>id 4285324155 статус active</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>id 4444968174 статус active</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>id 4124845206 статус active</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>id 4444712249 статус active</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>id 4444869727 статус rejected</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>id 4349334275 статус active</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>id 4285328953 статус active</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>id 4444524662 статус active</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>id 3965344207 статус active</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>id 4573121040 статус active</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>id 4253114863 статус active</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>id 3965207177 статус active</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>id 4125079566 статус active</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>id 3965211558 статус active</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>id 4253030337 статус active</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>id 4573102274 статус active</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>id 3965565847 статус active</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>id 4445119215 статус active</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>id 4189437762 статус active</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>id 4220978299 статус active</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>id 4125283125 статус active</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>id 4445230063 статус active</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>id 4285108577 статус active</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>id 4220729305 статус active</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>id 7260608738 статус active</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>id 4445242895 статус active</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>id 4124730141 статус active</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>id 4284950339 статус active</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>id 3965336925 статус active</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>id 4124828843 статус old</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>id 3964990179 статус old</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>id 4125257871 статус old</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>id 4284973404 статус active</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>id 4317088408 статус rejected</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>id 4316875109 статус active</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>id 4284733993 статус active</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>id 4572853508 статус active</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>id 4125224328 статус active</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>id 3965227267 статус rejected</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>нет цены без комиссии</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>на Авито цена как на маркетплейсах (7500); по правилу ≈ 3750</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>добавить plita-filtr-v2 = 3750 в data/avito_site_price_overrides.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>нет цены без комиссии</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>на Авито цена как на маркетплейсах (3990); по правилу ≈ 1995</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>добавить porshni-usil-pylniki-kryshki-v2 = 1995 в data/avito_site_price_overrides.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig-v2</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>нет цены без комиссии</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>на Авито цена как на маркетплейсах (2980); по правилу ≈ 1490</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>добавить pylniki-shtokov-orig-v2 = 1490 в data/avito_site_price_overrides.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>нет цены без комиссии</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>на Авито цена как на маркетплейсах (1490); по правилу ≈ 745</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>добавить salnik-shtoka-orig-v2 = 745 в data/avito_site_price_overrides.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>0am325025Y</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>нет в мастере</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>0am325025e</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>нет в мастере</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>0b5</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>нет в мастере</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>TEST001</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>jf015</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>нет в мастере</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Tilda</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>filtr-setka-0b5-orig</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>цена не равна половине</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Авито/сайт 745, половина маркетплейса 1175</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>оставить, если это сознательная цена</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>цена не равна половине</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Авито/сайт 925, половина маркетплейса 1490</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>оставить, если это сознательная цена</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>0AM325467J</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>0cw0am</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>0cw0am325025</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>0cw0amdsgdq200</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>0cw325025h</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Dq200dsg7</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>EA888</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>EA888gen3</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Ea888gen3</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>gidroakkumulyator-orig</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F203"/>
+  <autoFilter ref="A1:F130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7510,9 +5174,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -8141,9 +5805,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -9145,9 +6809,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -9482,9 +7146,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -9568,9 +7232,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -9654,9 +7318,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -9783,9 +7447,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -9826,9 +7490,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -9869,9 +7533,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -9912,9 +7576,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -10378,9 +8042,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -10421,9 +8085,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
@@ -10844,9 +8508,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -10887,9 +8551,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -10973,9 +8637,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -11145,9 +8809,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -11274,9 +8938,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
@@ -11317,9 +8981,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -11403,9 +9067,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -11446,9 +9110,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
@@ -11489,9 +9153,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -11575,9 +9239,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -11704,9 +9368,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
@@ -11833,9 +9497,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -12091,9 +9755,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -12177,9 +9841,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -12263,9 +9927,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F118" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -12349,9 +10013,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -12392,9 +10056,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -12435,9 +10099,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -12478,9 +10142,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -12521,9 +10185,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -12564,9 +10228,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
@@ -12607,9 +10271,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -12650,9 +10314,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
@@ -12822,9 +10486,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
@@ -12865,9 +10529,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -12908,9 +10572,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
@@ -12951,9 +10615,9 @@
           <t>есть</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>нет</t>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>есть</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$235</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26 / 77 / 26</t>
+          <t>26 / 183 / 25</t>
         </is>
       </c>
     </row>
@@ -535,61 +535,61 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Авито: объявление не из фида</t>
+          <t>Авито: цена</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Маркет: название</t>
+          <t>Авито: объявление не из фида</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Авито: ошибка автозагрузки</t>
+          <t>Маркет: название</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WB: название</t>
+          <t>Авито: ошибка автозагрузки</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>WB: название</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Авито/сайт: нет цены без комиссии</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -615,27 +615,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Авито: цена</t>
+          <t>WB: цена WB ≠ цена Ozon</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Авито/сайт: цена не равна половине</t>
+          <t>WB: цена</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WB: цена</t>
+          <t>Ozon: лишний</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ozon: лишний</t>
+          <t>Ozon: остаток</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ozon: остаток</t>
+          <t>Tilda: лишний</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -665,7 +665,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tilda: лишний</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -675,7 +675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>Маркет: лишний</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Маркет: лишний</t>
+          <t>Ozon: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -695,7 +695,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ozon: артикул отличается регистром</t>
+          <t>Tilda: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -705,7 +705,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tilda: артикул отличается регистром</t>
+          <t>WB: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -715,7 +715,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WB: артикул отличается регистром</t>
+          <t>Авито: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -725,7 +725,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Авито: артикул отличается регистром</t>
+          <t>Авито/сайт: цена не равна правилу</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1764,17 +1764,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена WB ≠ цена Ozon</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>WB: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254» ≠ мастер: «Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW п»</t>
+          <t>Ozon 78800, WB 3479 (4% от Ozon)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>выровнять: вписать цену Ozon в колонку «Цена WB» мастера и запустить update-cards</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WB: «Прокладки + сальники + пыльники DSG7 DQ200, Герман» ≠ мастер: «пыльники мехатроника DSG7 DQ200, оригинал Германия»</t>
+          <t>WB: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254» ≠ мастер: «Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW п»</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена WB ≠ цена Ozon</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 1450, WB 2479 (171% от Ozon)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>выровнять: вписать цену Ozon в колонку «Цена WB» мастера и запустить update-cards</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WB: «Оригинальные пластины на соленоиды VAG DSG7 DQ200» ≠ мастер: «Оригинальные пластины на соленоиды VAG DSG7 DQ200 »</t>
+          <t>WB: «Прокладки + сальники + пыльники DSG7 DQ200, Герман» ≠ мастер: «пыльники мехатроника DSG7 DQ200, оригинал Германия»</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита + фильтр DSG7 DQ200, комплект» ≠ мастер: «фильтр мехатроника DSG7 DQ200, комплект»</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита + фильтр + 2 пыльника штоков » ≠ мастер: «фильтр + 2 пыльника штоков DSG7 DQ200, комплект»</t>
+          <t>WB: «Оригинальные пластины на соленоиды VAG DSG7 DQ200» ≠ мастер: «Оригинальные пластины на соленоиды VAG DSG7 DQ200 »</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WB: «Усиленная плита + фильтр + 2 пыльника DSG7 DQ200, » ≠ мастер: «фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, к»</t>
+          <t>WB: «Усиленная гидроплита + фильтр DSG7 DQ200, комплект» ≠ мастер: «фильтр мехатроника DSG7 DQ200, комплект»</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита + фильтр + 2 пыльника DQ200» ≠ мастер: «фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полны»</t>
+          <t>WB: «Усиленная гидроплита + фильтр + 2 пыльника штоков » ≠ мастер: «фильтр + 2 пыльника штоков DSG7 DQ200, комплект»</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WB: «Усиленная плита + фильтр + 2 сальника DSG7 DQ200, » ≠ мастер: «фильтр + 2 оригинальных сальника VAG DSG7 DQ200, к»</t>
+          <t>WB: «Усиленная плита + фильтр + 2 пыльника DSG7 DQ200, » ≠ мастер: «фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, к»</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WB: «Комплект 4 толкателей вилок + 4 сальника DSG7 DQ20» ≠ мастер: «4 сальника DSG7 DQ200, на весь мехатроник»</t>
+          <t>WB: «Усиленная гидроплита + фильтр + 2 пыльника DQ200» ≠ мастер: «фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полны»</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WB: «Толкатели вилок + сальники + усиленные DSG7 DQ200» ≠ мастер: «усиленные алюминиевые сальники DSG7 DQ200, комплек»</t>
+          <t>WB: «Усиленная плита + фильтр + 2 сальника DSG7 DQ200, » ≠ мастер: «фильтр + 2 оригинальных сальника VAG DSG7 DQ200, к»</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2106,27 +2106,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 500</t>
+          <t>WB: «Комплект 4 толкателей вилок + 4 сальника DSG7 DQ20» ≠ мастер: «4 сальника DSG7 DQ200, на весь мехатроник»</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>update-cards</t>
         </is>
       </c>
     </row>
@@ -2138,27 +2138,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>WB: «Толкатели вилок + сальники + усиленные DSG7 DQ200» ≠ мастер: «усиленные алюминиевые сальники DSG7 DQ200, комплек»</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>update-cards</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2980</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1490</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2340,17 +2340,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2372,17 +2372,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2404,17 +2404,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2468,17 +2468,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2532,17 +2532,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2692,17 +2692,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2820,17 +2820,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2948,17 +2948,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>на Авито 2440 ≠ в нашем файле 3420</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2980,17 +2980,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3140,17 +3140,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3172,17 +3172,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3236,17 +3236,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3268,17 +3268,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3300,17 +3300,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3332,17 +3332,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3364,17 +3364,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3396,17 +3396,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3428,17 +3428,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3460,17 +3460,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>на Авито 725 ≠ в нашем файле 1010</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>на Авито 1240 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3652,17 +3652,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3748,17 +3748,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3780,17 +3780,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3802,27 +3802,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>нет цены без комиссии</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито цена как на маркетплейсах (7500); по правилу ≈ 3750</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>добавить plita-filtr-v2 = 3750 в data/avito_site_price_overrides.xlsx</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3834,27 +3834,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>нет цены без комиссии</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито цена как на маркетплейсах (3990); по правилу ≈ 1995</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>добавить porshni-usil-pylniki-kryshki-v2 = 1995 в data/avito_site_price_overrides.xlsx</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3866,27 +3866,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>нет цены без комиссии</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито цена как на маркетплейсах (2980); по правилу ≈ 1490</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>добавить pylniki-shtokov-orig-v2 = 1490 в data/avito_site_price_overrides.xlsx</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3898,27 +3898,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>нет цены без комиссии</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито цена как на маркетплейсах (1490); по правилу ≈ 745</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>добавить salnik-shtoka-orig-v2 = 745 в data/avito_site_price_overrides.xlsx</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3930,27 +3930,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3962,27 +3962,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3994,27 +3994,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4026,27 +4026,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4058,864 +4058,4224 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Dq500</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>WHT001922</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>filtr-dsg7-dq200</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>filtr-dsg7-dq500</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>gidroakkumulyator-orig</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>klipsy-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>kryshka-mehatronika-dq200</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>planka-solenoid-2sht</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>plastina-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-dq200-2sht</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-orig</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>plita-filtr-orig</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig-v2</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-dq200</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-niz-dq200</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-verh-dq200</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig-v2</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>salnikprivod-l</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>separatornaya-plastina-dq200</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>id 4284998704 статус active</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>id 4284880578 статус active</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>id 4220734432 статус active</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>id 4125069388 статус active</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>id 4284610725 статус active</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>id 4285296851 статус active</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>id 4284955885 статус active</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>id 4285324155 статус active</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DQ500 DSG7</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>id 4348814868 статус active</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>id 4349172359 статус active</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>id 4444968174 статус active</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>id 4124845206 статус active</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>id 4444712249 статус active</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>id 4444869727 статус rejected</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>id 4349334275 статус active</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>id 4285328953 статус active</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>id 4444524662 статус active</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>id 3965344207 статус active</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>id 4573121040 статус active</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>id 4253114863 статус active</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>id 3965207177 статус active</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>id 4125079566 статус active</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>id 3965211558 статус active</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>id 4253030337 статус active</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>id 4573102274 статус active</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>id 3965565847 статус active</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>id 4445119215 статус active</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>id 4189437762 статус active</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>id 4220978299 статус active</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>id 4125283125 статус active</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>id 4445230063 статус active</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>id 4285108577 статус active</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>id 4220729305 статус active</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>id 7260608738 статус active</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>id 4445242895 статус active</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>id 4124730141 статус active</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>id 4284950339 статус active</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>id 3965336925 статус active</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>id 4124828843 статус old</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>id 3964990179 статус old</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>id 4125257871 статус old</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>id 4284973404 статус active</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>id 4317088408 статус rejected</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>id 4316875109 статус active</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>id 4284733993 статус active</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>id 4572853508 статус active</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>id 4125224328 статус active</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>id 3965227267 статус rejected</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>0am325025Y</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>0am325025e</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>0b5</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
           <t>jf015</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>нет в мастере</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>0BH325183B</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>Ozon</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>артикул отличается регистром</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>0BH325183B</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>Tilda</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>артикул отличается регистром</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B213" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C213" t="inlineStr">
         <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>артикул отличается регистром</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F213" t="inlineStr">
         <is>
           <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>0BH325183B</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
         <is>
           <t>артикул отличается регистром</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F214" t="inlineStr">
         <is>
           <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>filtr-setka-0b5-orig</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
         <is>
           <t>Авито/сайт</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>цена не равна половине</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Авито/сайт 745, половина маркетплейса 1175</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>цена не равна правилу</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
         <is>
           <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="4" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>цена не равна половине</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Авито/сайт 925, половина маркетплейса 1490</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>оставить, если это сознательная цена</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>0AM325467J</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>0AM325467J</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>0AM325473</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>0am325025</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>0cw0am</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>0cw0am</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>0cw0am325025</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>0cw0am325025</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>0cw0amdsgdq200</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>0cw0amdsgdq200</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>0cw325025h</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>0cw325025h</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>31705-1XF1A</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>31705-X428B</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>317053TX0C</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Dq200dsg7</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>EA888</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>EA888</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>EA888gen3</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>EA888gen3</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Ea888gen3</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="4" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
         <is>
           <t>НИЗКО</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Ea888gen3</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>gidroakkumulyator-orig</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>gidroakkumulyator-orig</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F130"/>
+  <autoFilter ref="A1:F235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$223</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26 / 183 / 25</t>
+          <t>27 / 170 / 25</t>
         </is>
       </c>
     </row>
@@ -575,57 +575,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WB: название</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>Маркет: нет в мастере</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Маркет: нет в мастере</t>
+          <t>Авито: нет на площадке</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Авито: нет на площадке</t>
+          <t>WB: цена</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WB: цена WB ≠ цена Ozon</t>
+          <t>Ozon: лишний</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WB: цена</t>
+          <t>Ozon: остаток</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -635,7 +635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ozon: лишний</t>
+          <t>Tilda: лишний</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ozon: остаток</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tilda: лишний</t>
+          <t>Маркет: лишний</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -665,7 +665,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>Ozon: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -675,7 +675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Маркет: лишний</t>
+          <t>Tilda: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ozon: артикул отличается регистром</t>
+          <t>WB: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -695,7 +695,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tilda: артикул отличается регистром</t>
+          <t>Авито: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -705,30 +705,10 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WB: артикул отличается регистром</t>
+          <t>Авито/сайт: цена не равна правилу</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Авито: артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Авито/сайт: цена не равна правилу</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -743,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -826,7 +806,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -836,17 +816,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>WB 2478.6 ≠ мастер 1450</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -858,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -873,7 +853,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -890,7 +870,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -922,7 +902,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -937,7 +917,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -954,7 +934,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -969,7 +949,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -986,7 +966,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1001,7 +981,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1018,7 +998,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1033,7 +1013,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1050,7 +1030,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1065,7 +1045,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1082,27 +1062,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1094,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1129,7 +1109,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1146,7 +1126,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1178,7 +1158,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1210,7 +1190,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1242,7 +1222,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1252,17 +1232,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1254,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1289,7 +1269,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1306,7 +1286,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1338,7 +1318,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1348,17 +1328,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1350,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1402,7 +1382,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1434,7 +1414,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1466,7 +1446,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1498,7 +1478,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1530,7 +1510,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1562,7 +1542,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1594,59 +1574,59 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>salniki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>ошибка автозагрузки</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>TEST001</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1638,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1668,17 +1648,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1690,27 +1670,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 50 ≠ мастер 0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1722,27 +1702,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WB: «Прокладки электронной платы DSG7 DQ200 0AM927769N» ≠ мастер: «Электронная плата мехатроника DSG7 DQ200 0AM927769»</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1734,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1764,17 +1744,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>цена WB ≠ цена Ozon</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ozon 78800, WB 3479 (4% от Ozon)</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>выровнять: вписать цену Ozon в колонку «Цена WB» мастера и запустить update-cards</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1786,27 +1766,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>WB: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254» ≠ мастер: «Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW п»</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -1818,27 +1798,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>цена WB ≠ цена Ozon</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ozon 1450, WB 2479 (171% от Ozon)</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>выровнять: вписать цену Ozon в колонку «Цена WB» мастера и запустить update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -1850,27 +1830,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WB: «Прокладки + сальники + пыльники DSG7 DQ200, Герман» ≠ мастер: «пыльники мехатроника DSG7 DQ200, оригинал Германия»</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -1882,27 +1862,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -1914,27 +1894,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WB: «Оригинальные пластины на соленоиды VAG DSG7 DQ200» ≠ мастер: «Оригинальные пластины на соленоиды VAG DSG7 DQ200 »</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -1946,27 +1926,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита + фильтр DSG7 DQ200, комплект» ≠ мастер: «фильтр мехатроника DSG7 DQ200, комплект»</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -1978,27 +1958,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита + фильтр + 2 пыльника штоков » ≠ мастер: «фильтр + 2 пыльника штоков DSG7 DQ200, комплект»</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2010,27 +1990,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WB: «Усиленная плита + фильтр + 2 пыльника DSG7 DQ200, » ≠ мастер: «фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, к»</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2042,27 +2022,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WB: «Усиленная гидроплита + фильтр + 2 пыльника DQ200» ≠ мастер: «фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полны»</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2074,27 +2054,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WB: «Усиленная плита + фильтр + 2 сальника DSG7 DQ200, » ≠ мастер: «фильтр + 2 оригинальных сальника VAG DSG7 DQ200, к»</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2106,27 +2086,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WB: «Комплект 4 толкателей вилок + 4 сальника DSG7 DQ20» ≠ мастер: «4 сальника DSG7 DQ200, на весь мехатроник»</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2138,27 +2118,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WB: «Толкатели вилок + сальники + усиленные DSG7 DQ200» ≠ мастер: «усиленные алюминиевые сальники DSG7 DQ200, комплек»</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2150,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2185,7 +2165,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2202,7 +2182,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2217,7 +2197,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2234,7 +2214,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2249,7 +2229,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2266,7 +2246,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2281,7 +2261,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2298,7 +2278,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2313,7 +2293,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2330,7 +2310,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2345,7 +2325,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2362,7 +2342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2377,7 +2357,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2394,7 +2374,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2409,7 +2389,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2426,7 +2406,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2441,7 +2421,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2458,7 +2438,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2473,7 +2453,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2490,7 +2470,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2505,7 +2485,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2522,7 +2502,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2537,7 +2517,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2554,7 +2534,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2569,7 +2549,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 2440 ≠ в нашем файле 3420</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2586,7 +2566,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2601,7 +2581,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2618,7 +2598,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2633,7 +2613,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2650,7 +2630,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2665,7 +2645,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2682,7 +2662,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2697,7 +2677,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2714,7 +2694,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2729,7 +2709,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2746,7 +2726,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2761,7 +2741,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2778,7 +2758,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2793,7 +2773,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2810,7 +2790,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2825,7 +2805,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2842,7 +2822,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2857,7 +2837,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2874,7 +2854,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2889,7 +2869,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2906,7 +2886,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2921,7 +2901,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2938,7 +2918,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2953,7 +2933,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 3420</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2970,7 +2950,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2985,7 +2965,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3002,7 +2982,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3017,7 +2997,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3034,7 +3014,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3049,7 +3029,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3066,7 +3046,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3081,7 +3061,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3098,7 +3078,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3113,7 +3093,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3130,7 +3110,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3145,7 +3125,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3162,7 +3142,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3177,7 +3157,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3194,7 +3174,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3209,7 +3189,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 725 ≠ в нашем файле 1010</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3226,7 +3206,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3241,7 +3221,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 1240 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3258,7 +3238,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3273,7 +3253,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3290,7 +3270,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3305,7 +3285,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3322,7 +3302,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3337,7 +3317,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3354,7 +3334,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3369,7 +3349,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3386,7 +3366,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3401,7 +3381,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3418,7 +3398,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3433,7 +3413,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3450,7 +3430,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3465,7 +3445,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3482,7 +3462,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3497,7 +3477,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3514,7 +3494,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3529,7 +3509,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3546,7 +3526,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3561,7 +3541,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3578,7 +3558,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3588,17 +3568,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1010</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3620,17 +3600,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 1740</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3622,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3657,7 +3637,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3674,7 +3654,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3689,7 +3669,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3706,7 +3686,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3721,7 +3701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3738,7 +3718,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3753,7 +3733,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3770,7 +3750,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3785,7 +3765,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3802,7 +3782,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3834,7 +3814,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3849,7 +3829,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3866,7 +3846,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3881,7 +3861,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3898,7 +3878,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3913,7 +3893,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3930,7 +3910,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3945,7 +3925,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3962,7 +3942,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3972,17 +3952,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3974,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4004,17 +3984,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4026,7 +4006,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4041,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4058,7 +4038,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4073,7 +4053,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4090,7 +4070,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4105,7 +4085,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4122,7 +4102,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4137,7 +4117,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4154,7 +4134,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4169,7 +4149,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4186,7 +4166,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4201,7 +4181,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4218,7 +4198,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4233,7 +4213,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4250,7 +4230,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4265,7 +4245,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4282,7 +4262,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4297,7 +4277,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4314,7 +4294,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4329,7 +4309,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4326,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4361,7 +4341,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4378,7 +4358,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4393,7 +4373,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4410,7 +4390,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4425,7 +4405,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4442,7 +4422,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4457,7 +4437,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4474,7 +4454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4489,7 +4469,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4506,7 +4486,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4521,7 +4501,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4538,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4553,7 +4533,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4570,7 +4550,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4585,7 +4565,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4602,7 +4582,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4617,7 +4597,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4634,7 +4614,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4649,7 +4629,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4666,7 +4646,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4681,7 +4661,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4698,7 +4678,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4713,7 +4693,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4730,7 +4710,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4745,7 +4725,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4762,7 +4742,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4777,7 +4757,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4794,7 +4774,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4809,7 +4789,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4826,7 +4806,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4841,7 +4821,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4858,7 +4838,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4873,7 +4853,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4890,7 +4870,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4905,7 +4885,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4922,7 +4902,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4937,7 +4917,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4954,7 +4934,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4969,7 +4949,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4986,7 +4966,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5001,7 +4981,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5018,7 +4998,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5033,7 +5013,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5050,7 +5030,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5065,7 +5045,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5082,7 +5062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5097,7 +5077,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5114,7 +5094,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5129,7 +5109,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5146,7 +5126,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5161,7 +5141,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5178,7 +5158,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5193,7 +5173,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5210,7 +5190,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5225,7 +5205,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5242,7 +5222,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5257,7 +5237,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5274,7 +5254,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5289,7 +5269,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5306,7 +5286,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5321,7 +5301,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5338,7 +5318,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5353,7 +5333,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5370,7 +5350,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5385,7 +5365,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5402,7 +5382,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5412,17 +5392,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5414,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5444,17 +5424,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5446,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5476,17 +5456,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5478,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5508,17 +5488,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5510,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5540,17 +5520,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5542,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5572,17 +5552,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5574,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5604,17 +5584,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5606,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5636,17 +5616,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5638,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5668,17 +5648,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5670,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5700,17 +5680,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5702,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5732,17 +5712,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5734,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5764,17 +5744,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5766,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5801,7 +5781,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5818,7 +5798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5833,7 +5813,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5850,7 +5830,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5865,7 +5845,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5882,7 +5862,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5897,7 +5877,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5914,7 +5894,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5929,7 +5909,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5946,7 +5926,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5961,7 +5941,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5978,7 +5958,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5993,7 +5973,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6010,7 +5990,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6025,7 +6005,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6042,7 +6022,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6057,7 +6037,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6074,7 +6054,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6089,7 +6069,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6106,7 +6086,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6121,7 +6101,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6138,7 +6118,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6153,7 +6133,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6170,7 +6150,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6185,7 +6165,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6202,7 +6182,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6217,7 +6197,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6234,7 +6214,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6249,7 +6229,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6266,7 +6246,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6281,7 +6261,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6298,7 +6278,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6313,7 +6293,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6330,7 +6310,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6345,7 +6325,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6362,7 +6342,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6377,7 +6357,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6394,7 +6374,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6409,7 +6389,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6426,7 +6406,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6441,7 +6421,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6458,7 +6438,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6473,7 +6453,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6490,7 +6470,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6505,7 +6485,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6522,7 +6502,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6537,7 +6517,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6554,7 +6534,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6569,7 +6549,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6586,7 +6566,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6601,7 +6581,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6618,7 +6598,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6633,7 +6613,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6650,7 +6630,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6665,7 +6645,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6682,7 +6662,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6697,7 +6677,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6714,7 +6694,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6729,7 +6709,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6746,7 +6726,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6761,7 +6741,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6778,7 +6758,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6793,7 +6773,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6810,7 +6790,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6825,7 +6805,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6842,7 +6822,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6857,7 +6837,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6874,7 +6854,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6889,7 +6869,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 4125224328 статус active</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6906,7 +6886,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6921,7 +6901,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 3965227267 статус rejected</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6938,27 +6918,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>0am325025Y</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -6970,27 +6950,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>0am325025e</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7002,27 +6982,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7034,27 +7014,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -7066,135 +7046,135 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>jf015</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7204,125 +7184,125 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7332,29 +7312,29 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7364,29 +7344,29 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7396,29 +7376,29 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7428,29 +7408,29 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>jf015</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7460,17 +7440,17 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7482,27 +7462,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7514,27 +7494,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7546,27 +7526,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7578,27 +7558,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7610,27 +7590,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>цена не равна правилу</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>оставить, если это сознательная цена</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7622,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7657,7 +7637,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7674,7 +7654,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7689,7 +7669,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -7706,7 +7686,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7721,7 +7701,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -7738,7 +7718,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7753,7 +7733,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -7770,7 +7750,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7785,7 +7765,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -7802,7 +7782,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7817,7 +7797,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -7834,7 +7814,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7849,7 +7829,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -7866,7 +7846,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7881,7 +7861,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -7890,392 +7870,8 @@
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>0cw325025h</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Dq200dsg7</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>EA888</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>EA888gen3</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Ea888gen3</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>gidroakkumulyator-orig</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F235"/>
+  <autoFilter ref="A1:F223"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$222</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27 / 170 / 25</t>
+          <t>26 / 170 / 25</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -723,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F223"/>
+  <dimension ref="A1:F222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -806,7 +806,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WB 2478.6 ≠ мастер 1450</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1062,27 +1062,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1232,17 +1232,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1328,17 +1328,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1599,34 +1599,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 50 ≠ мастер 0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1670,27 +1670,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1734,27 +1734,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 2440 ≠ в нашем файле 3420</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 3420</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 725 ≠ в нашем файле 1720</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1010</t>
+          <t>на Авито 1240 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 1740</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3600,17 +3600,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5360,17 +5360,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>id 4125224328 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>id 3965227267 статус rejected</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6886,27 +6886,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>0am325025Y</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>0am325025e</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6992,17 +6992,17 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>jf015</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7024,49 +7024,49 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>jf015</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7174,27 +7174,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
@@ -7206,27 +7206,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>цена не равна правилу</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>оставить, если это сознательная цена</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>31705-1XF1A</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
+          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -7838,40 +7838,8 @@
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>gidroakkumulyator-orig</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F223"/>
+  <autoFilter ref="A1:F222"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10224,7 +10192,7 @@
         <v>11</v>
       </c>
       <c r="D56" t="n">
-        <v>1450</v>
+        <v>2450</v>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$234</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26 / 170 / 25</t>
+          <t>26 / 182 / 25</t>
         </is>
       </c>
     </row>
@@ -575,57 +575,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>Ozon: лишний</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Маркет: нет в мастере</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Авито: нет на площадке</t>
+          <t>Маркет: нет в мастере</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WB: цена</t>
+          <t>Авито: нет на площадке</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ozon: лишний</t>
+          <t>Ozon: остаток</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ozon: остаток</t>
+          <t>WB: цена</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -723,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F222"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WB 4160 ≠ мастер 1990</t>
+          <t>WB 2164.24 ≠ мастер 1990</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1616,17 +1616,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 14 ≠ мастер 13</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1702,27 +1702,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 50 ≠ мастер 0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1734,27 +1734,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1766,27 +1766,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1798,27 +1798,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1830,27 +1830,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1862,27 +1862,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1894,27 +1894,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1926,27 +1926,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1958,27 +1958,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1990,27 +1990,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2022,27 +2022,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2054,27 +2054,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2086,27 +2086,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 3420</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 2440 ≠ в нашем файле 3420</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1720</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 1740</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>на Авито 725 ≠ в нашем файле 1720</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3568,17 +3568,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 1240 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3952,17 +3952,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5360,17 +5360,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5392,17 +5392,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5424,17 +5424,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5488,17 +5488,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5520,17 +5520,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5616,17 +5616,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5648,17 +5648,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5670,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5712,17 +5712,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6886,27 +6886,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6918,27 +6918,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6950,27 +6950,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6982,27 +6982,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7014,411 +7014,411 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>id 4125257871 статус old</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>id 4284973404 статус active</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>id 4317088408 статус rejected</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>id 4316875109 статус active</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>id 4284733993 статус active</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>id 4572853508 статус active</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>id 4125224328 статус active</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>id 3965227267 статус rejected</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>0am325025Y</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>0am325025e</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>0b5</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
           <t>jf015</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>нет в мастере</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Tilda</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>цена не равна правилу</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>оставить, если это сознательная цена</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>0AM325467J</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>0cw0am</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>0cw0am325025</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7430,27 +7430,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7462,27 +7462,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7494,27 +7494,27 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7526,27 +7526,27 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7558,27 +7558,27 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>31705-1XF1A</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -7814,32 +7814,416 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
+          <t>0cw0amdsgdq200</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>0cw325025h</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>31705-1XF1A</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>31705-X428B</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>317053TX0C</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>EA888</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>EA888gen3</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Ea888gen3</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
           <t>gidroakkumulyator-orig</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C234" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F234" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F222"/>
+  <autoFilter ref="A1:F234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8767,9 +9151,9 @@
       <c r="D22" t="n">
         <v>3879</v>
       </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -11900,9 +12284,9 @@
       <c r="D96" t="n">
         <v>7500</v>
       </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -12115,9 +12499,9 @@
       <c r="D101" t="n">
         <v>9500</v>
       </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -12201,9 +12585,9 @@
       <c r="D103" t="n">
         <v>7500</v>
       </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
@@ -12244,9 +12628,9 @@
       <c r="D104" t="n">
         <v>8500</v>
       </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -12287,9 +12671,9 @@
       <c r="D105" t="n">
         <v>9500</v>
       </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -12416,9 +12800,9 @@
       <c r="D108" t="n">
         <v>3990</v>
       </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
@@ -12760,9 +13144,9 @@
       <c r="D116" t="n">
         <v>2850</v>
       </c>
-      <c r="E116" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
@@ -12846,9 +13230,9 @@
       <c r="D118" t="n">
         <v>1490</v>
       </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -12889,9 +13273,9 @@
       <c r="D119" t="n">
         <v>1490</v>
       </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -13362,9 +13746,9 @@
       <c r="D130" t="n">
         <v>5700</v>
       </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26 / 182 / 25</t>
+          <t>25 / 183 / 25</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -625,7 +625,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WB: цена</t>
+          <t>Tilda: лишний</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -635,7 +635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tilda: лишний</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>Маркет: лишний</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Маркет: лишний</t>
+          <t>Ozon: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -665,7 +665,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ozon: артикул отличается регистром</t>
+          <t>Tilda: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -675,7 +675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tilda: артикул отличается регистром</t>
+          <t>WB: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WB: артикул отличается регистром</t>
+          <t>Авито: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -695,20 +695,10 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Авито: артикул отличается регистром</t>
+          <t>Авито/сайт: цена не равна правилу</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Авито/сайт: цена не равна правилу</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -774,7 +764,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -784,17 +774,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WB 2164.24 ≠ мастер 1990</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -806,7 +796,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -821,7 +811,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -838,7 +828,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -870,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -885,7 +875,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -902,7 +892,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -917,7 +907,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -934,7 +924,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -949,7 +939,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -966,7 +956,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -981,7 +971,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -998,7 +988,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1013,7 +1003,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1030,27 +1020,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1052,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1077,7 +1067,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1094,7 +1084,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1126,7 +1116,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1158,7 +1148,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1190,7 +1180,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1200,17 +1190,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1212,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1237,7 +1227,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1254,7 +1244,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1286,7 +1276,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1296,17 +1286,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1308,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1350,7 +1340,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1382,7 +1372,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1414,7 +1404,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1446,7 +1436,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1478,7 +1468,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1510,7 +1500,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1542,7 +1532,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1567,34 +1557,34 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>Ozon 14 ≠ мастер 13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1596,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1616,17 +1606,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ozon 14 ≠ мастер 13</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1628,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1670,7 +1660,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1680,17 +1670,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 50 ≠ мастер 0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1692,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1712,17 +1702,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1724,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1766,7 +1756,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1798,7 +1788,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1830,7 +1820,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1862,7 +1852,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1894,7 +1884,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12843,9 +12833,9 @@
       <c r="D109" t="n">
         <v>3990</v>
       </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>есть</t>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>лишний</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$251</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25 / 183 / 25</t>
+          <t>43 / 184 / 23</t>
         </is>
       </c>
     </row>
@@ -555,87 +555,87 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Маркет: название</t>
+          <t>WB: цена</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Авито: ошибка автозагрузки</t>
+          <t>Маркет: название</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ozon: лишний</t>
+          <t>Авито: ошибка автозагрузки</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>Ozon: лишний</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Маркет: нет в мастере</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Авито: нет на площадке</t>
+          <t>Маркет: нет в мастере</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ozon: остаток</t>
+          <t>Авито: нет на площадке</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tilda: лишний</t>
+          <t>Ozon: остаток</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>Tilda: лишний</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Маркет: лишний</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ozon: артикул отличается регистром</t>
+          <t>Маркет: лишний</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -665,7 +665,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tilda: артикул отличается регистром</t>
+          <t>Ozon: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -675,7 +675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WB: артикул отличается регистром</t>
+          <t>Tilda: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Авито: артикул отличается регистром</t>
+          <t>WB: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -695,10 +695,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Авито: артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Авито/сайт: цена не равна правилу</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -713,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -764,7 +774,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -774,17 +784,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>WB 1633.1 ≠ мастер 5879</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -796,7 +806,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>02E305045E</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -806,17 +816,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>WB 1354.25 ≠ мастер 1571.48</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -828,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,17 +848,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>WB 1232 ≠ мастер 3850</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -860,7 +870,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -875,7 +885,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -892,7 +902,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -907,7 +917,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -924,7 +934,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -939,7 +949,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -956,7 +966,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -966,17 +976,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>WB 928.27 ≠ мастер 980</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -988,7 +998,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -998,17 +1008,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>WB 1149.64 ≠ мастер 1290</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1020,27 +1030,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>WB 1738.4 ≠ мастер 1950</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1052,27 +1062,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 437.06 ≠ мастер 490</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1084,27 +1094,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 883.95 ≠ мастер 980</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1116,27 +1126,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 6684.64 ≠ мастер 7500</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1158,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 8467.32 ≠ мастер 9500</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1190,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1195,12 +1205,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1212,27 +1222,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>WB 7612.2 ≠ мастер 8500</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1254,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1259,12 +1269,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1276,27 +1286,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1308,27 +1318,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 1230 ≠ мастер 1380</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1340,27 +1350,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 757.79 ≠ мастер 840</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1372,27 +1382,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 522.9 ≠ мастер 580</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1404,27 +1414,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 522.9 ≠ мастер 580</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1436,27 +1446,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1468,27 +1478,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1500,27 +1510,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 437.06 ≠ мастер 490</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1532,603 +1542,603 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WB 1667.06 ≠ мастер 1870</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>push-wb-price</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>цена</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>WB 5080.72 ≠ мастер 5700</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>push-wb-price</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0AM325473</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0am325025G</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0am325025С</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0ambset</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0cw0amdsgdq200</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EA888</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>нет на площадке</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>остаток 13</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EA888gen3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>нет на площадке</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>остаток 9</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ea888gen3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>нет на площадке</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>остаток 9</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig-v2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>salniki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>ошибка автозагрузки</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>0AM325587E</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>остаток</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Ozon 14 ≠ мастер 13</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>push-stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0BH325</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>TEST001</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>korpus-filtra-0bh325159</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>остаток</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Ozon 50 ≠ мастер 0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>push-stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>remkomplekt-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>TEST001</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Tilda</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>TESTWB001</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>01X301127C</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2140,27 +2150,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>Ozon 13 ≠ мастер 12</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -2172,27 +2182,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>Ozon 14 ≠ мастер 13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -2204,27 +2214,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2236,27 +2246,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2268,27 +2278,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>Ozon 50 ≠ мастер 0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -2300,27 +2310,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2332,27 +2342,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2364,27 +2374,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2396,27 +2406,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2428,27 +2438,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2460,27 +2470,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2492,27 +2502,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2524,27 +2534,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2556,27 +2566,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2588,27 +2598,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2620,27 +2630,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2652,27 +2662,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2684,27 +2694,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2726,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2731,7 +2741,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2748,7 +2758,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2763,7 +2773,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2780,7 +2790,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2795,7 +2805,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2812,7 +2822,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2827,7 +2837,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2844,7 +2854,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2859,7 +2869,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2876,7 +2886,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2891,7 +2901,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 3420</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2908,7 +2918,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2923,7 +2933,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2940,7 +2950,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2955,7 +2965,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2972,7 +2982,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2987,7 +2997,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3004,7 +3014,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3019,7 +3029,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3036,7 +3046,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3051,7 +3061,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3068,7 +3078,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3083,7 +3093,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3100,7 +3110,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3115,7 +3125,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3132,7 +3142,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3147,7 +3157,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3164,7 +3174,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3179,7 +3189,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3196,7 +3206,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3211,7 +3221,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3228,7 +3238,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3243,7 +3253,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3260,7 +3270,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3275,7 +3285,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3292,7 +3302,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3307,7 +3317,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3324,7 +3334,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3339,7 +3349,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3356,7 +3366,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3371,7 +3381,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3388,7 +3398,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3403,7 +3413,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3420,7 +3430,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3435,7 +3445,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3452,7 +3462,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3467,7 +3477,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3484,7 +3494,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3499,7 +3509,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 2440 ≠ в нашем файле 3420</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3516,7 +3526,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3531,7 +3541,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1720</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3548,7 +3558,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3563,7 +3573,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 1740</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3580,7 +3590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3595,7 +3605,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3612,7 +3622,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3627,7 +3637,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3644,7 +3654,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3659,7 +3669,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3676,7 +3686,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3691,7 +3701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3708,7 +3718,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3723,7 +3733,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3740,7 +3750,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3755,7 +3765,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3772,7 +3782,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3787,7 +3797,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3804,7 +3814,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3819,7 +3829,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3836,7 +3846,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3851,7 +3861,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3868,7 +3878,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3883,7 +3893,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3900,7 +3910,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3910,17 +3920,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3942,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3942,17 +3952,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3974,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3979,7 +3989,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +4006,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4011,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4028,7 +4038,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4043,7 +4053,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4060,7 +4070,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4075,7 +4085,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4092,7 +4102,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4107,7 +4117,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4124,7 +4134,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4139,7 +4149,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 725 ≠ в нашем файле 1720</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4156,7 +4166,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4171,7 +4181,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 1240 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4188,7 +4198,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4203,7 +4213,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4220,7 +4230,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4235,7 +4245,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4252,7 +4262,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4267,7 +4277,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4284,7 +4294,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4299,7 +4309,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4316,7 +4326,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4331,7 +4341,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4348,7 +4358,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4363,7 +4373,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4380,7 +4390,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4395,7 +4405,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4412,7 +4422,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4427,7 +4437,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4444,7 +4454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4459,7 +4469,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4476,7 +4486,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4491,7 +4501,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4508,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4518,17 +4528,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4550,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4550,17 +4560,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4582,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4587,7 +4597,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4604,7 +4614,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4619,7 +4629,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4636,7 +4646,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4651,7 +4661,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4668,7 +4678,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4683,7 +4693,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4700,7 +4710,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4715,7 +4725,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4732,7 +4742,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4747,7 +4757,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4764,7 +4774,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4779,7 +4789,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4796,7 +4806,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4811,7 +4821,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4828,7 +4838,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4843,7 +4853,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4860,7 +4870,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4875,7 +4885,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4892,7 +4902,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4907,7 +4917,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4924,7 +4934,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4939,7 +4949,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4956,7 +4966,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4971,7 +4981,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4988,7 +4998,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5003,7 +5013,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5020,7 +5030,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5035,7 +5045,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5052,7 +5062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5067,7 +5077,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5084,7 +5094,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5099,7 +5109,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5116,7 +5126,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5131,7 +5141,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5148,7 +5158,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5163,7 +5173,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5180,7 +5190,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5195,7 +5205,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5212,7 +5222,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5227,7 +5237,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5244,7 +5254,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5259,7 +5269,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5276,7 +5286,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5291,7 +5301,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5308,7 +5318,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5323,7 +5333,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5340,7 +5350,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5355,7 +5365,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5372,7 +5382,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5387,7 +5397,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5404,7 +5414,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5419,7 +5429,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5436,7 +5446,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5451,7 +5461,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5468,7 +5478,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5483,7 +5493,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5500,7 +5510,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5515,7 +5525,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5532,7 +5542,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5547,7 +5557,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5564,7 +5574,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5579,7 +5589,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5596,7 +5606,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5611,7 +5621,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5628,7 +5638,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5643,7 +5653,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5660,7 +5670,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5675,7 +5685,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5692,7 +5702,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5707,7 +5717,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5724,7 +5734,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5734,17 +5744,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5766,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5766,17 +5776,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5798,17 +5808,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5830,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5830,17 +5840,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5862,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5862,17 +5872,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5894,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5894,17 +5904,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5926,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5926,17 +5936,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5958,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5958,17 +5968,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5990,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5990,17 +6000,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6022,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6022,17 +6032,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6054,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6054,17 +6064,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6086,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6086,17 +6096,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6118,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6118,17 +6128,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6150,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6150,17 +6160,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6182,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6182,17 +6192,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6214,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6214,17 +6224,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6246,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6246,17 +6256,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6278,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6278,17 +6288,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6310,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6310,17 +6320,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6342,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6347,7 +6357,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6364,7 +6374,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6379,7 +6389,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6396,7 +6406,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6411,7 +6421,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6428,7 +6438,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6443,7 +6453,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6460,7 +6470,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6475,7 +6485,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6492,7 +6502,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6507,7 +6517,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6524,7 +6534,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6539,7 +6549,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6556,7 +6566,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6571,7 +6581,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6588,7 +6598,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6603,7 +6613,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6620,7 +6630,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6635,7 +6645,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6652,7 +6662,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6667,7 +6677,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6684,7 +6694,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6699,7 +6709,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6716,7 +6726,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6731,7 +6741,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6748,7 +6758,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6763,7 +6773,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6780,7 +6790,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6795,7 +6805,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6812,7 +6822,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6827,7 +6837,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6844,7 +6854,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6859,7 +6869,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6876,7 +6886,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6891,7 +6901,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6908,7 +6918,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6923,7 +6933,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -6940,7 +6950,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6955,7 +6965,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -6972,7 +6982,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6987,7 +6997,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7004,7 +7014,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7019,7 +7029,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7036,7 +7046,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7051,7 +7061,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7068,7 +7078,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7083,7 +7093,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7100,7 +7110,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7115,7 +7125,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7132,7 +7142,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7147,7 +7157,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7164,7 +7174,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7179,7 +7189,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7196,7 +7206,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7211,7 +7221,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7228,7 +7238,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7243,7 +7253,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7260,27 +7270,27 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7292,27 +7302,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7324,27 +7334,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7356,27 +7366,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7388,635 +7398,635 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>id 7260608738 статус active</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>id 4445242895 статус active</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>id 4124730141 статус active</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>id 4284950339 статус active</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>id 3965336925 статус active</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>id 4124828843 статус old</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>id 3964990179 статус old</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>id 4125257871 статус old</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>id 4284973404 статус active</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>id 4317088408 статус rejected</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>id 4316875109 статус active</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>id 4284733993 статус active</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>id 4572853508 статус active</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>id 4125224328 статус active</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>id 3965227267 статус rejected</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>0am325025Y</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>0am325025e</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>0b5</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
           <t>jf015</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>нет в мастере</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F228" t="inlineStr">
         <is>
           <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Tilda</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>цена не равна правилу</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>оставить, если это сознательная цена</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>0AM325467J</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>0cw0am</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>0cw0am325025</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>0cw0amdsgdq200</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>0cw325025h</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -8028,27 +8038,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -8060,27 +8070,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -8092,27 +8102,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -8124,27 +8134,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Маркет: «Магнит + алюминиевый корпус фильтра EA888 Gen.3, к» ≠ мастер: «Комплект: алюминиевый корпус (крышка) масляного фи»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -8156,27 +8166,27 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
@@ -8188,7 +8198,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8203,7 +8213,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроаккумулятор мехатроника DSG7 DQ200 VAG rebuil» ≠ мастер: «Восстановленный гидроаккумулятор мехатроника DSG7 »</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8212,8 +8222,552 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>0AM325473</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>0am325025</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>0am325477ae</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>0cw0am</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>0cw0am325025</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>0cw0amdsgdq200</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>0cw325025h</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>31705-1XF1A</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>31705-X428B</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>317053TX0C</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>EA888</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Ea888gen3</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F234"/>
+  <autoFilter ref="A1:F251"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$233</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>43 / 184 / 23</t>
+          <t>25 / 184 / 23</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WB: цена</t>
+          <t>Маркет: название</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -565,57 +565,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Маркет: название</t>
+          <t>Авито: ошибка автозагрузки</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Авито: ошибка автозагрузки</t>
+          <t>Ozon: лишний</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ozon: лишний</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>Маркет: нет в мастере</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Маркет: нет в мастере</t>
+          <t>Авито: нет на площадке</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Авито: нет на площадке</t>
+          <t>Ozon: остаток</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -625,17 +625,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ozon: остаток</t>
+          <t>Tilda: лишний</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tilda: лишний</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>Маркет: лишний</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Маркет: лишний</t>
+          <t>Ozon: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -665,7 +665,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ozon: артикул отличается регистром</t>
+          <t>Tilda: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -675,7 +675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tilda: артикул отличается регистром</t>
+          <t>WB: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WB: артикул отличается регистром</t>
+          <t>Авито: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -695,20 +695,10 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Авито: артикул отличается регистром</t>
+          <t>Авито/сайт: цена не равна правилу</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Авито/сайт: цена не равна правилу</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -723,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F251"/>
+  <dimension ref="A1:F233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -774,7 +764,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -784,17 +774,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WB 1633.1 ≠ мастер 5879</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -806,7 +796,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>02E305045E</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,17 +806,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WB 1354.25 ≠ мастер 1571.48</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -838,7 +828,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -848,17 +838,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WB 1232 ≠ мастер 3850</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -870,7 +860,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -885,7 +875,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -902,7 +892,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -917,7 +907,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -934,7 +924,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -949,7 +939,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -966,7 +956,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -976,17 +966,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WB 928.27 ≠ мастер 980</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -998,7 +988,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1008,17 +998,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WB 1149.64 ≠ мастер 1290</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1030,27 +1020,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>WB 1738.4 ≠ мастер 1950</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1062,27 +1052,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WB 437.06 ≠ мастер 490</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1094,27 +1084,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WB 883.95 ≠ мастер 980</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1116,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WB 6684.64 ≠ мастер 7500</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1158,27 +1148,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WB 8467.32 ≠ мастер 9500</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1180,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1205,12 +1195,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1222,27 +1212,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>WB 7612.2 ≠ мастер 8500</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1244,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1269,12 +1259,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1286,27 +1276,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1318,27 +1308,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>WB 1230 ≠ мастер 1380</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1350,27 +1340,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WB 757.79 ≠ мастер 840</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1382,27 +1372,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>WB 522.9 ≠ мастер 580</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1414,27 +1404,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>WB 522.9 ≠ мастер 580</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1446,27 +1436,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1478,27 +1468,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1510,27 +1500,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>WB 437.06 ≠ мастер 490</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1542,603 +1532,603 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0AM325025B</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>остаток</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ozon 13 ≠ мастер 12</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>push-stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0AM325587E</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>остаток</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Ozon 14 ≠ мастер 13</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>push-stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0BH325</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>остаток</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Ozon 50 ≠ мастер 0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>push-stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig-v2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tilda</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TESTWB001</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>WB</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>WB 1667.06 ≠ мастер 1870</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>push-wb-price</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>WB 5080.72 ≠ мастер 5700</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>push-wb-price</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0am325025G</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>0am325025С</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0ambset</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>0cw0amdsgdq200</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>EA888</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>остаток 13</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>EA888gen3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>остаток 9</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Ea888gen3</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>нет на площадке</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>остаток 9</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>filtr-setka-0b5-orig</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-orig</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>plita-filtr-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2150,27 +2140,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ozon 13 ≠ мастер 12</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2182,27 +2172,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ozon 14 ≠ мастер 13</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2214,27 +2204,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2246,27 +2236,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2278,27 +2268,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2310,27 +2300,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2342,27 +2332,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2374,27 +2364,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2406,27 +2396,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2438,27 +2428,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2470,27 +2460,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2502,27 +2492,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2534,27 +2524,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2566,27 +2556,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2598,27 +2588,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2630,27 +2620,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2662,27 +2652,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2694,27 +2684,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2716,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2741,7 +2731,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2758,7 +2748,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2773,7 +2763,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2790,7 +2780,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2805,7 +2795,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2822,7 +2812,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2837,7 +2827,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2854,7 +2844,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2869,7 +2859,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2886,7 +2876,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2901,7 +2891,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2918,7 +2908,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2933,7 +2923,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>на Авито 2440 ≠ в нашем файле 3420</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2950,7 +2940,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2965,7 +2955,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2982,7 +2972,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2997,7 +2987,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3014,7 +3004,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3029,7 +3019,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3046,7 +3036,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3061,7 +3051,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3078,7 +3068,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3093,7 +3083,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3110,7 +3100,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3125,7 +3115,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3142,7 +3132,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3157,7 +3147,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3174,7 +3164,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3189,7 +3179,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3206,7 +3196,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3221,7 +3211,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3238,7 +3228,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3253,7 +3243,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3270,7 +3260,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3285,7 +3275,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3302,7 +3292,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3317,7 +3307,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3334,7 +3324,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3349,7 +3339,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3366,7 +3356,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3381,7 +3371,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3398,7 +3388,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3413,7 +3403,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3430,7 +3420,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3445,7 +3435,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3462,7 +3452,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3477,7 +3467,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3494,7 +3484,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3509,7 +3499,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 3420</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3526,7 +3516,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3541,7 +3531,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3558,7 +3548,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3573,7 +3563,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 725 ≠ в нашем файле 1720</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3590,7 +3580,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3605,7 +3595,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 1240 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3622,7 +3612,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3637,7 +3627,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3654,7 +3644,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3669,7 +3659,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3686,7 +3676,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3701,7 +3691,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3718,7 +3708,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3733,7 +3723,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3750,7 +3740,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3765,7 +3755,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3782,7 +3772,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3797,7 +3787,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3814,7 +3804,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3829,7 +3819,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3846,7 +3836,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3861,7 +3851,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3878,7 +3868,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3893,7 +3883,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3910,7 +3900,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3925,7 +3915,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3942,7 +3932,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3952,17 +3942,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3964,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3984,17 +3974,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4006,7 +3996,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4011,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4038,7 +4028,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4053,7 +4043,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4070,7 +4060,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4085,7 +4075,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4102,7 +4092,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4117,7 +4107,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4134,7 +4124,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4149,7 +4139,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1720</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4166,7 +4156,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4181,7 +4171,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 1740</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4198,7 +4188,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4213,7 +4203,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4230,7 +4220,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4245,7 +4235,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4262,7 +4252,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4277,7 +4267,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4294,7 +4284,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4309,7 +4299,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4326,7 +4316,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4341,7 +4331,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4358,7 +4348,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4373,7 +4363,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4390,7 +4380,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4405,7 +4395,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4422,7 +4412,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,7 +4427,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4454,7 +4444,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4469,7 +4459,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4486,7 +4476,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4501,7 +4491,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4518,7 +4508,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4528,17 +4518,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4540,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4560,17 +4550,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4572,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4597,7 +4587,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4614,7 +4604,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4629,7 +4619,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4646,7 +4636,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4661,7 +4651,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4678,7 +4668,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4693,7 +4683,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4710,7 +4700,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4725,7 +4715,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4742,7 +4732,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4757,7 +4747,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4774,7 +4764,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4789,7 +4779,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4806,7 +4796,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4821,7 +4811,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4838,7 +4828,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4853,7 +4843,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4870,7 +4860,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4885,7 +4875,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4902,7 +4892,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4917,7 +4907,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4934,7 +4924,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4949,7 +4939,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4966,7 +4956,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4981,7 +4971,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4998,7 +4988,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5013,7 +5003,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5030,7 +5020,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5045,7 +5035,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5062,7 +5052,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5077,7 +5067,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5094,7 +5084,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5109,7 +5099,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5126,7 +5116,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5141,7 +5131,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5158,7 +5148,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5173,7 +5163,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5190,7 +5180,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5205,7 +5195,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5222,7 +5212,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5237,7 +5227,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5254,7 +5244,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5269,7 +5259,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5286,7 +5276,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5301,7 +5291,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5318,7 +5308,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5333,7 +5323,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5350,7 +5340,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5365,7 +5355,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5382,7 +5372,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5397,7 +5387,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5414,7 +5404,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5429,7 +5419,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5446,7 +5436,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5461,7 +5451,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5478,7 +5468,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5493,7 +5483,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5510,7 +5500,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5525,7 +5515,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5542,7 +5532,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5557,7 +5547,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5574,7 +5564,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5589,7 +5579,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5606,7 +5596,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5621,7 +5611,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5638,7 +5628,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5653,7 +5643,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5670,7 +5660,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5685,7 +5675,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5702,7 +5692,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5717,7 +5707,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5734,7 +5724,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5749,7 +5739,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5766,7 +5756,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5776,17 +5766,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5788,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5808,17 +5798,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5820,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5840,17 +5830,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5862,7 +5852,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5872,17 +5862,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5884,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5904,17 +5894,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5916,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5936,17 +5926,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5948,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5968,17 +5958,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5980,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6000,17 +5990,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6012,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6032,17 +6022,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6044,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6064,17 +6054,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6076,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6096,17 +6086,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6108,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6128,17 +6118,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6140,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6160,17 +6150,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6172,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6192,17 +6182,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6204,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6224,17 +6214,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6236,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6256,17 +6246,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6268,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6288,17 +6278,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6300,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6320,17 +6310,17 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6332,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6357,7 +6347,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6374,7 +6364,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6389,7 +6379,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6406,7 +6396,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6421,7 +6411,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6438,7 +6428,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6453,7 +6443,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6470,7 +6460,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6485,7 +6475,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6502,7 +6492,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6517,7 +6507,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6534,7 +6524,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6549,7 +6539,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6566,7 +6556,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6581,7 +6571,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6598,7 +6588,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6613,7 +6603,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6630,7 +6620,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6645,7 +6635,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6662,7 +6652,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6677,7 +6667,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6694,7 +6684,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6709,7 +6699,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6726,7 +6716,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6741,7 +6731,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6758,7 +6748,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6773,7 +6763,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6790,7 +6780,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6805,7 +6795,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6822,7 +6812,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6837,7 +6827,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6854,7 +6844,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6869,7 +6859,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6886,7 +6876,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6901,7 +6891,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6918,7 +6908,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6933,7 +6923,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -6950,7 +6940,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6965,7 +6955,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -6982,7 +6972,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6997,7 +6987,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7014,7 +7004,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7029,7 +7019,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7046,7 +7036,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7061,7 +7051,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7078,7 +7068,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7093,7 +7083,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7110,7 +7100,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7125,7 +7115,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7142,7 +7132,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7157,7 +7147,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7174,7 +7164,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7189,7 +7179,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7206,7 +7196,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7221,7 +7211,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7238,7 +7228,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7253,7 +7243,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 4125224328 статус active</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7270,7 +7260,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7285,7 +7275,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 3965227267 статус rejected</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7302,27 +7292,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>0am325025Y</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7334,27 +7324,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>0am325025e</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7366,27 +7356,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7398,27 +7388,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -7430,135 +7420,135 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>jf015</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7568,317 +7558,317 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7888,29 +7878,29 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7920,29 +7910,29 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7952,29 +7942,29 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7984,29 +7974,29 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>jf015</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8016,17 +8006,17 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -8038,27 +8028,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -8070,27 +8060,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -8102,27 +8092,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -8134,27 +8124,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -8166,608 +8156,32 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>цена не равна правилу</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>оставить, если это сознательная цена</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>0AM325467J</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>0cw0am</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>0cw0am325025</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>0cw0amdsgdq200</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>0cw325025h</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Dq200dsg7</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>EA888</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Ea888gen3</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F251"/>
+  <autoFilter ref="A1:F233"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$244</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25 / 184 / 23</t>
+          <t>36 / 184 / 23</t>
         </is>
       </c>
     </row>
@@ -585,37 +585,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>WB: цена</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Маркет: нет в мастере</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Авито: нет на площадке</t>
+          <t>Маркет: нет в мастере</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ozon: остаток</t>
+          <t>Авито: нет на площадке</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -625,17 +625,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tilda: лишний</t>
+          <t>Ozon: остаток</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>Ozon: цена</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Маркет: лишний</t>
+          <t>Tilda: лишний</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ozon: артикул отличается регистром</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -665,7 +665,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tilda: артикул отличается регистром</t>
+          <t>Маркет: лишний</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -675,7 +675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WB: артикул отличается регистром</t>
+          <t>Ozon: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Авито: артикул отличается регистром</t>
+          <t>Tilda: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -695,10 +695,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>WB: артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Авито: артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Авито/сайт: цена не равна правилу</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -713,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F233"/>
+  <dimension ref="A1:F244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -764,27 +784,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>Ozon 2479 ≠ мастер 2860</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
         </is>
       </c>
     </row>
@@ -796,7 +816,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -806,17 +826,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>WB 3478.75 ≠ мастер 4130</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -828,7 +848,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,17 +858,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>WB 1989.89 ≠ мастер 2540</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -860,7 +880,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -870,17 +890,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>WB 4878.93 ≠ мастер 6050</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -892,7 +912,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -902,17 +922,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>WB 980 ≠ мастер 1240</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -924,7 +944,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -934,17 +954,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>WB 1479.13 ≠ мастер 1880</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -956,7 +976,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -966,17 +986,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>WB 980 ≠ мастер 1240</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -988,7 +1008,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -998,17 +1018,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>WB 2879.07 ≠ мастер 3620</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1020,27 +1040,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>WB 2479 ≠ мастер 2860</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1052,27 +1072,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 1290 ≠ мастер 1610</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1084,27 +1104,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>WB 1489.83 ≠ мастер 1620</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-wb-price</t>
         </is>
       </c>
     </row>
@@ -1116,27 +1136,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1168,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1200,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1195,12 +1215,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1232,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1227,12 +1247,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1264,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1259,12 +1279,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1276,27 +1296,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1308,27 +1328,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1340,27 +1360,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1392,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1387,7 +1407,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1404,7 +1424,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1436,7 +1456,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1468,7 +1488,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1500,7 +1520,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1532,379 +1552,379 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>EA888</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>нет на площадке</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>остаток 13</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EA888gen3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>нет на площадке</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>остаток 9</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ea888gen3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>нет на площадке</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>остаток 9</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig-v2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>salniki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>ошибка автозагрузки</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>0AM325025B</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>остаток</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Ozon 13 ≠ мастер 12</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>push-stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0AM325587E</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>остаток</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Ozon 14 ≠ мастер 13</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>push-stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0BH325</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>TEST001</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>korpus-filtra-0bh325159</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>остаток</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Ozon 50 ≠ мастер 0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>push-stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1936,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1926,17 +1946,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 13 ≠ мастер 12</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1968,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1958,17 +1978,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 14 ≠ мастер 13</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2000,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2012,7 +2032,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2044,7 +2064,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2054,17 +2074,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 50 ≠ мастер 0</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2096,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2108,12 +2128,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2140,27 +2160,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2172,27 +2192,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2204,27 +2224,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2236,27 +2256,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2268,27 +2288,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2300,27 +2320,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2332,27 +2352,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2364,27 +2384,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2396,27 +2416,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2428,27 +2448,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2460,27 +2480,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2512,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2507,7 +2527,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2524,7 +2544,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2539,7 +2559,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2556,7 +2576,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2571,7 +2591,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2588,7 +2608,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2603,7 +2623,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2620,7 +2640,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2635,7 +2655,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2652,7 +2672,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2667,7 +2687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2684,7 +2704,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2699,7 +2719,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2716,7 +2736,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2731,7 +2751,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2748,7 +2768,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2763,7 +2783,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 1740 ≠ в нашем файле 2890</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2780,7 +2800,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2795,7 +2815,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2812,7 +2832,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2827,7 +2847,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2844,7 +2864,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2859,7 +2879,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 995 ≠ в нашем файле 1780</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2876,7 +2896,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2891,7 +2911,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2908,7 +2928,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2923,7 +2943,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 3420</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2940,7 +2960,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2955,7 +2975,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2972,7 +2992,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2987,7 +3007,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3004,7 +3024,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3019,7 +3039,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3036,7 +3056,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3051,7 +3071,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3068,7 +3088,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3083,7 +3103,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3100,7 +3120,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3115,7 +3135,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3132,7 +3152,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3147,7 +3167,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3164,7 +3184,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3179,7 +3199,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3196,7 +3216,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3211,7 +3231,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3228,7 +3248,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3243,7 +3263,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3260,7 +3280,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3275,7 +3295,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 2440 ≠ в нашем файле 4240</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3292,7 +3312,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3307,7 +3327,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3324,7 +3344,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3339,7 +3359,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3356,7 +3376,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3371,7 +3391,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3388,7 +3408,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3403,7 +3423,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3420,7 +3440,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3435,7 +3455,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3452,7 +3472,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3467,7 +3487,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3484,7 +3504,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3499,7 +3519,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 490 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3516,7 +3536,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3531,7 +3551,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 740 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3548,7 +3568,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3563,7 +3583,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1720</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3580,7 +3600,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3595,7 +3615,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 1740</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3612,7 +3632,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3627,7 +3647,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3644,7 +3664,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3659,7 +3679,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3676,7 +3696,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3691,7 +3711,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3708,7 +3728,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3723,7 +3743,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 490 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3740,7 +3760,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3755,7 +3775,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3772,7 +3792,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3787,7 +3807,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1440 ≠ в нашем файле 2530</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3804,7 +3824,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3819,7 +3839,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3836,7 +3856,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3851,7 +3871,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3868,7 +3888,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3883,7 +3903,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3900,7 +3920,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3915,7 +3935,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>на Авито 725 ≠ в нашем файле 1720</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3932,7 +3952,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3942,17 +3962,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>на Авито 1240 ≠ в нашем файле 2000</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3984,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3974,17 +3994,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -3996,7 +4016,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4011,7 +4031,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4028,7 +4048,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4043,7 +4063,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4060,7 +4080,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4075,7 +4095,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 645 ≠ в нашем файле 1130</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4092,7 +4112,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4107,7 +4127,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4124,7 +4144,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4156,7 +4176,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4171,7 +4191,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 745 ≠ в нашем файле 1130</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4188,7 +4208,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4203,7 +4223,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4220,7 +4240,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4235,7 +4255,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4252,7 +4272,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4267,7 +4287,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4284,7 +4304,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4294,17 +4314,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4336,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4326,17 +4346,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4368,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4363,7 +4383,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4380,7 +4400,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4395,7 +4415,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4412,7 +4432,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4427,7 +4447,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4444,7 +4464,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4459,7 +4479,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4476,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4491,7 +4511,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4508,7 +4528,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4523,7 +4543,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4540,7 +4560,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4555,7 +4575,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4572,7 +4592,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4587,7 +4607,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4604,7 +4624,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4619,7 +4639,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4636,7 +4656,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4651,7 +4671,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4668,7 +4688,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4683,7 +4703,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4700,7 +4720,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4715,7 +4735,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4732,7 +4752,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4747,7 +4767,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4764,7 +4784,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4779,7 +4799,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4796,7 +4816,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4811,7 +4831,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4828,7 +4848,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4843,7 +4863,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4860,7 +4880,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4875,7 +4895,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4892,7 +4912,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4907,7 +4927,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4924,7 +4944,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4939,7 +4959,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4956,7 +4976,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4971,7 +4991,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4988,7 +5008,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5003,7 +5023,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5020,7 +5040,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5035,7 +5055,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5052,7 +5072,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5067,7 +5087,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5084,7 +5104,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5099,7 +5119,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5116,7 +5136,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5131,7 +5151,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5148,7 +5168,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5163,7 +5183,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5180,7 +5200,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5195,7 +5215,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5212,7 +5232,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5227,7 +5247,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5244,7 +5264,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5259,7 +5279,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5276,7 +5296,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5291,7 +5311,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5308,7 +5328,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5323,7 +5343,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5340,7 +5360,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5355,7 +5375,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5372,7 +5392,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5387,7 +5407,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5404,7 +5424,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5419,7 +5439,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5436,7 +5456,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5451,7 +5471,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5468,7 +5488,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5483,7 +5503,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5500,7 +5520,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5515,7 +5535,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5532,7 +5552,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5547,7 +5567,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5564,7 +5584,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5579,7 +5599,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5596,7 +5616,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5611,7 +5631,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5628,7 +5648,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5643,7 +5663,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5660,7 +5680,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5675,7 +5695,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5692,7 +5712,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5707,7 +5727,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5724,7 +5744,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5739,7 +5759,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5756,7 +5776,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5766,17 +5786,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5808,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5798,17 +5818,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5840,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5830,17 +5850,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5872,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5862,17 +5882,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5904,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5894,17 +5914,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5936,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5926,17 +5946,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5968,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5958,17 +5978,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5980,7 +6000,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5990,17 +6010,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6032,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6022,17 +6042,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6064,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6054,17 +6074,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6096,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6086,17 +6106,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6128,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6123,7 +6143,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6140,7 +6160,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6155,7 +6175,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6172,7 +6192,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6187,7 +6207,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6204,7 +6224,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6219,7 +6239,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6236,7 +6256,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6251,7 +6271,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6268,7 +6288,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6283,7 +6303,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6300,7 +6320,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6315,7 +6335,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6332,7 +6352,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6347,7 +6367,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6364,7 +6384,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6379,7 +6399,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6396,7 +6416,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6411,7 +6431,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6428,7 +6448,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6443,7 +6463,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6460,7 +6480,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6475,7 +6495,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6492,7 +6512,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6507,7 +6527,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6524,7 +6544,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6539,7 +6559,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6556,7 +6576,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6571,7 +6591,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6588,7 +6608,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6603,7 +6623,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6620,7 +6640,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6635,7 +6655,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6652,7 +6672,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6667,7 +6687,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6684,7 +6704,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6699,7 +6719,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6716,7 +6736,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6731,7 +6751,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6748,7 +6768,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6763,7 +6783,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6780,7 +6800,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6795,7 +6815,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6812,7 +6832,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6827,7 +6847,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6844,7 +6864,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6859,7 +6879,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6876,7 +6896,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6891,7 +6911,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6908,7 +6928,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6923,7 +6943,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -6940,7 +6960,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6955,7 +6975,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -6972,7 +6992,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6987,7 +7007,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7004,7 +7024,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7019,7 +7039,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7036,7 +7056,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7051,7 +7071,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7068,7 +7088,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7083,7 +7103,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7100,7 +7120,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7115,7 +7135,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7132,7 +7152,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7147,7 +7167,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7164,7 +7184,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7179,7 +7199,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7196,7 +7216,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7211,7 +7231,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7228,7 +7248,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7243,7 +7263,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7260,7 +7280,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7275,7 +7295,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7292,27 +7312,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7324,27 +7344,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7356,27 +7376,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7388,27 +7408,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7420,379 +7440,379 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>id 4284973404 статус active</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>id 4317088408 статус rejected</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>id 4316875109 статус active</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>id 4284733993 статус active</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>id 4572853508 статус active</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>id 4125224328 статус active</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>id 3965227267 статус rejected</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>0am325025Y</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>0am325025e</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>0b5</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
           <t>jf015</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>нет в мастере</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Tilda</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>цена не равна правилу</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>оставить, если это сознательная цена</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>0AM325467J</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>0am325025</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>0cw0am</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7804,27 +7824,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7836,27 +7856,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7868,27 +7888,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7900,27 +7920,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7932,27 +7952,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7984,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>31705-1XF1A</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7979,7 +7999,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -7996,7 +8016,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8011,7 +8031,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8028,7 +8048,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8043,7 +8063,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8060,7 +8080,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8075,7 +8095,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8092,7 +8112,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8107,7 +8127,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8124,7 +8144,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8139,7 +8159,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8156,32 +8176,384 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
+          <t>0cw0am325025</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>0cw0amdsgdq200</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>0cw325025h</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>31705-1XF0C</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>31705-1XF1A</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>31705-X428B</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>317053TX0C</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Dq200dsg70am0cw</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>EA888</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
           <t>Ea888gen3</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F244" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F233"/>
+  <autoFilter ref="A1:F244"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8684,7 +9056,7 @@
         <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>3479</v>
+        <v>4130</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -8813,7 +9185,7 @@
         <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>1990</v>
+        <v>2540</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -9638,7 +10010,7 @@
         <v>21</v>
       </c>
       <c r="D35" t="n">
-        <v>4879</v>
+        <v>6050</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -9939,7 +10311,7 @@
         <v>251</v>
       </c>
       <c r="D42" t="n">
-        <v>979</v>
+        <v>1240</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
@@ -9982,7 +10354,7 @@
         <v>141</v>
       </c>
       <c r="D43" t="n">
-        <v>1479</v>
+        <v>1880</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -10276,7 +10648,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="n">
-        <v>979</v>
+        <v>1240</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
@@ -10362,7 +10734,7 @@
         <v>229</v>
       </c>
       <c r="D52" t="n">
-        <v>2879</v>
+        <v>3620</v>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
@@ -10577,7 +10949,7 @@
         <v>56</v>
       </c>
       <c r="D57" t="n">
-        <v>2479</v>
+        <v>2860</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
@@ -10792,7 +11164,7 @@
         <v>149</v>
       </c>
       <c r="D62" t="n">
-        <v>1290</v>
+        <v>1610</v>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
@@ -10921,7 +11293,7 @@
         <v>60</v>
       </c>
       <c r="D65" t="n">
-        <v>1490</v>
+        <v>1620</v>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$234</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36 / 184 / 23</t>
+          <t>26 / 184 / 23</t>
         </is>
       </c>
     </row>
@@ -585,37 +585,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WB: цена</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>Маркет: нет в мастере</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Маркет: нет в мастере</t>
+          <t>Авито: нет на площадке</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Авито: нет на площадке</t>
+          <t>Ozon: остаток</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -625,17 +625,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ozon: остаток</t>
+          <t>Ozon: цена</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ozon: цена</t>
+          <t>Tilda: лишний</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tilda: лишний</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>Маркет: лишний</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -665,7 +665,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Маркет: лишний</t>
+          <t>Ozon: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -675,7 +675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ozon: артикул отличается регистром</t>
+          <t>Tilda: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tilda: артикул отличается регистром</t>
+          <t>WB: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -695,7 +695,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WB: артикул отличается регистром</t>
+          <t>Авито: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -705,20 +705,10 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Авито: артикул отличается регистром</t>
+          <t>Авито/сайт: цена не равна правилу</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Авито/сайт: цена не равна правилу</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -733,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F244"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -816,7 +806,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -826,17 +816,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WB 3478.75 ≠ мастер 4130</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -848,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -858,17 +848,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WB 1989.89 ≠ мастер 2540</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -880,7 +870,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -890,17 +880,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WB 4878.93 ≠ мастер 6050</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -912,7 +902,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -922,17 +912,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WB 980 ≠ мастер 1240</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -944,7 +934,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -954,17 +944,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>WB 1479.13 ≠ мастер 1880</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -976,7 +966,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -986,17 +976,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WB 980 ≠ мастер 1240</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1008,7 +998,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1018,17 +1008,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WB 2879.07 ≠ мастер 3620</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1030,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1050,17 +1040,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>WB 2479 ≠ мастер 2860</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1072,27 +1062,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WB 1290 ≠ мастер 1610</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1094,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>WB 1489.83 ≠ мастер 1620</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>push-wb-price</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1126,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1168,27 +1158,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1200,27 +1190,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1222,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1247,12 +1237,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1254,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1279,12 +1269,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1286,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1311,12 +1301,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1328,27 +1318,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1360,27 +1350,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1382,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1407,7 +1397,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1424,7 +1414,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1456,7 +1446,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1488,7 +1478,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1520,7 +1510,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1552,7 +1542,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1562,17 +1552,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1574,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1594,337 +1584,337 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Ozon 13 ≠ мастер 12</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>Ozon 14 ≠ мастер 13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>0BH325</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>остаток</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ozon 50 ≠ мастер 0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>push-stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>plita-filtr</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-orig</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>plita-filtr-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>plita-filtr-v2</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1926,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1946,17 +1936,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ozon 13 ≠ мастер 12</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1958,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1978,17 +1968,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ozon 14 ≠ мастер 13</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2000,7 +1990,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2032,7 +2022,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2064,7 +2054,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2074,17 +2064,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2086,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2128,12 +2118,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2160,12 +2150,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2192,27 +2182,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2224,27 +2214,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2256,27 +2246,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2288,27 +2278,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2320,27 +2310,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2352,27 +2342,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2374,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2416,27 +2406,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2448,27 +2438,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 1740 ≠ в нашем файле 2890</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2480,27 +2470,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2502,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2527,7 +2517,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2544,7 +2534,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2559,7 +2549,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>на Авито 995 ≠ в нашем файле 1780</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2576,7 +2566,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2591,7 +2581,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2608,7 +2598,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2623,7 +2613,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2640,7 +2630,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2655,7 +2645,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2672,7 +2662,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2687,7 +2677,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2704,7 +2694,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2719,7 +2709,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2736,7 +2726,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2751,7 +2741,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2768,7 +2758,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2783,7 +2773,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2890</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2800,7 +2790,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2815,7 +2805,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2832,7 +2822,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2847,7 +2837,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2864,7 +2854,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2879,7 +2869,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1780</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2896,7 +2886,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2911,7 +2901,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2928,7 +2918,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2943,7 +2933,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2960,7 +2950,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2975,7 +2965,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>на Авито 2440 ≠ в нашем файле 4240</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2992,7 +2982,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3007,7 +2997,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3024,7 +3014,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3039,7 +3029,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3056,7 +3046,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3071,7 +3061,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3088,7 +3078,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3103,7 +3093,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3120,7 +3110,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3135,7 +3125,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3152,7 +3142,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3167,7 +3157,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3184,7 +3174,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3199,7 +3189,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 490 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3216,7 +3206,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3231,7 +3221,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 740 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3248,7 +3238,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3263,7 +3253,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3280,7 +3270,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3295,7 +3285,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 4240</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3312,7 +3302,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3327,7 +3317,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3344,7 +3334,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3359,7 +3349,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3376,7 +3366,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3391,7 +3381,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3408,7 +3398,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3423,7 +3413,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3440,7 +3430,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3472,7 +3462,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3487,7 +3477,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 1440 ≠ в нашем файле 2530</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3504,7 +3494,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3519,7 +3509,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 870</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3536,7 +3526,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3551,7 +3541,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1320</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3568,7 +3558,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3583,7 +3573,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3600,7 +3590,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3615,7 +3605,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 725 ≠ в нашем файле 1720</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3632,7 +3622,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3647,7 +3637,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 1240 ≠ в нашем файле 2000</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3664,7 +3654,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3679,7 +3669,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3696,7 +3686,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3711,7 +3701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3728,7 +3718,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3743,7 +3733,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 870</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3760,7 +3750,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3775,7 +3765,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 645 ≠ в нашем файле 1130</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3792,7 +3782,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3807,7 +3797,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2530</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3824,7 +3814,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3839,7 +3829,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3856,7 +3846,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3871,7 +3861,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 745 ≠ в нашем файле 1130</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3888,7 +3878,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3903,7 +3893,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3920,7 +3910,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3935,7 +3925,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1720</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3952,7 +3942,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3967,7 +3957,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 2000</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3984,7 +3974,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3994,17 +3984,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4006,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4026,17 +4016,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4038,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4063,7 +4053,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4080,7 +4070,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4095,7 +4085,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 1130</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4112,7 +4102,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4127,7 +4117,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4144,7 +4134,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4159,7 +4149,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4176,7 +4166,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4191,7 +4181,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1130</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4208,7 +4198,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4223,7 +4213,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4240,7 +4230,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4255,7 +4245,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4272,7 +4262,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4287,7 +4277,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4304,7 +4294,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4314,17 +4304,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4326,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4346,17 +4336,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4358,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4383,7 +4373,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4400,7 +4390,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4415,7 +4405,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4432,7 +4422,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4447,7 +4437,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4464,7 +4454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4479,7 +4469,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4496,7 +4486,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4528,7 +4518,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4543,7 +4533,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4560,7 +4550,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4575,7 +4565,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4592,7 +4582,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4607,7 +4597,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4624,7 +4614,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4639,7 +4629,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4656,7 +4646,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4671,7 +4661,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4688,7 +4678,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4703,7 +4693,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4720,7 +4710,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4735,7 +4725,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4752,7 +4742,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4767,7 +4757,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4784,7 +4774,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4799,7 +4789,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4816,7 +4806,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4831,7 +4821,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4848,7 +4838,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4863,7 +4853,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4880,7 +4870,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4895,7 +4885,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4912,7 +4902,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4927,7 +4917,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4944,7 +4934,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4959,7 +4949,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4976,7 +4966,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4991,7 +4981,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5008,7 +4998,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5023,7 +5013,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5040,7 +5030,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5055,7 +5045,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5072,7 +5062,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5087,7 +5077,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5104,7 +5094,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5119,7 +5109,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5136,7 +5126,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5151,7 +5141,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5168,7 +5158,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5183,7 +5173,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5200,7 +5190,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5215,7 +5205,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5232,7 +5222,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5247,7 +5237,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5264,7 +5254,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5279,7 +5269,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5296,7 +5286,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5311,7 +5301,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5328,7 +5318,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5343,7 +5333,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5360,7 +5350,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5375,7 +5365,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5392,7 +5382,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5407,7 +5397,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5424,7 +5414,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5439,7 +5429,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5456,7 +5446,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5471,7 +5461,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5488,7 +5478,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5503,7 +5493,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5520,7 +5510,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5535,7 +5525,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5552,7 +5542,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5567,7 +5557,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5584,7 +5574,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5599,7 +5589,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5616,7 +5606,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5631,7 +5621,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5648,7 +5638,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5663,7 +5653,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5680,7 +5670,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5695,7 +5685,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5712,7 +5702,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5727,7 +5717,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5744,7 +5734,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5759,7 +5749,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5776,7 +5766,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5791,7 +5781,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5808,7 +5798,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5818,17 +5808,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5830,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5850,17 +5840,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5862,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5882,17 +5872,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5894,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5914,17 +5904,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5926,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5946,17 +5936,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5958,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5978,17 +5968,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6000,7 +5990,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6010,17 +6000,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6022,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6042,17 +6032,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6054,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6074,17 +6064,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6086,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6106,17 +6096,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6118,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6143,7 +6133,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6160,7 +6150,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6175,7 +6165,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6192,7 +6182,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6207,7 +6197,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6224,7 +6214,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6239,7 +6229,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6256,7 +6246,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6271,7 +6261,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6288,7 +6278,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6303,7 +6293,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6320,7 +6310,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6335,7 +6325,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6352,7 +6342,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6367,7 +6357,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6384,7 +6374,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6399,7 +6389,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6416,7 +6406,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6431,7 +6421,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6448,7 +6438,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6463,7 +6453,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6480,7 +6470,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6495,7 +6485,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6512,7 +6502,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6527,7 +6517,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6544,7 +6534,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6559,7 +6549,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6576,7 +6566,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6591,7 +6581,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6608,7 +6598,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6623,7 +6613,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6640,7 +6630,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6655,7 +6645,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6672,7 +6662,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6687,7 +6677,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6704,7 +6694,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6719,7 +6709,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6736,7 +6726,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6751,7 +6741,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6768,7 +6758,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6783,7 +6773,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6800,7 +6790,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6815,7 +6805,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6832,7 +6822,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6847,7 +6837,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6864,7 +6854,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6879,7 +6869,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6896,7 +6886,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6911,7 +6901,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6928,7 +6918,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6943,7 +6933,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -6960,7 +6950,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6975,7 +6965,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -6992,7 +6982,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7007,7 +6997,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7024,7 +7014,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7039,7 +7029,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7056,7 +7046,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7071,7 +7061,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7088,7 +7078,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7103,7 +7093,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7120,7 +7110,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7135,7 +7125,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7152,7 +7142,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7167,7 +7157,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7184,7 +7174,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7199,7 +7189,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7216,7 +7206,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7231,7 +7221,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7248,7 +7238,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7263,7 +7253,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7280,7 +7270,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7295,7 +7285,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>id 4125224328 статус active</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7312,7 +7302,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7327,7 +7317,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>id 3965227267 статус rejected</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7344,27 +7334,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>0am325025Y</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7376,27 +7366,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>0am325025e</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7408,27 +7398,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7440,27 +7430,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -7472,135 +7462,135 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>jf015</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7610,61 +7600,61 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7674,29 +7664,29 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7706,29 +7696,29 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7738,29 +7728,29 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7770,29 +7760,29 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>jf015</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7802,17 +7792,17 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7824,27 +7814,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7856,27 +7846,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7888,27 +7878,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7920,27 +7910,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>артикул отличается регистром</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7952,27 +7942,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>цена не равна правилу</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>оставить, если это сознательная цена</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7974,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7999,7 +7989,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8016,7 +8006,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8031,7 +8021,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8048,7 +8038,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8063,7 +8053,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8080,7 +8070,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8095,7 +8085,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8112,7 +8102,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8127,7 +8117,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8144,7 +8134,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8159,7 +8149,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8176,7 +8166,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8191,7 +8181,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8208,7 +8198,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -8223,7 +8213,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8232,328 +8222,8 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>0cw325025h</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Dq200dsg7</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>EA888</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Ea888gen3</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F244"/>
+  <autoFilter ref="A1:F234"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$235</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26 / 184 / 23</t>
+          <t>26 / 185 / 23</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>WB: название</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Маркет: лишний</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -665,7 +665,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ozon: артикул отличается регистром</t>
+          <t>Маркет: лишний</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -675,7 +675,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tilda: артикул отличается регистром</t>
+          <t>Ozon: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -685,7 +685,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WB: артикул отличается регистром</t>
+          <t>Tilda: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -695,7 +695,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Авито: артикул отличается регистром</t>
+          <t>WB: артикул отличается регистром</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -705,10 +705,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Авито: артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Авито/сайт: цена не равна правилу</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -723,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2150,7 +2160,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2160,17 +2170,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>WB: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie »</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>update-cards</t>
         </is>
       </c>
     </row>
@@ -2182,27 +2192,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2224,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2229,7 +2239,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2246,7 +2256,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2261,7 +2271,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2278,7 +2288,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2293,7 +2303,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2310,7 +2320,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2325,7 +2335,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2342,7 +2352,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2357,7 +2367,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2374,7 +2384,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2389,7 +2399,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2406,7 +2416,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2421,7 +2431,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2438,7 +2448,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2453,7 +2463,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2890</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2470,7 +2480,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2485,7 +2495,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1740 ≠ в нашем файле 2890</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2502,7 +2512,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2517,7 +2527,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2534,7 +2544,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2549,7 +2559,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1780</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2566,7 +2576,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2581,7 +2591,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 995 ≠ в нашем файле 1780</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2598,7 +2608,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2613,7 +2623,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2630,7 +2640,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2645,7 +2655,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2662,7 +2672,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2677,7 +2687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2694,7 +2704,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2709,7 +2719,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2726,7 +2736,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2758,7 +2768,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2773,7 +2783,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2790,7 +2800,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2805,7 +2815,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2822,7 +2832,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2837,7 +2847,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2854,7 +2864,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2869,7 +2879,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2886,7 +2896,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2901,7 +2911,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2918,7 +2928,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2933,7 +2943,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2950,7 +2960,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2965,7 +2975,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 4240</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2982,7 +2992,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2997,7 +3007,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 2440 ≠ в нашем файле 4240</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3014,7 +3024,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3029,7 +3039,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3046,7 +3056,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3061,7 +3071,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3078,7 +3088,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3093,7 +3103,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3110,7 +3120,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3125,7 +3135,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3142,7 +3152,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3157,7 +3167,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3174,7 +3184,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3189,7 +3199,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 870</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3206,7 +3216,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3221,7 +3231,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1320</t>
+          <t>на Авито 490 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3238,7 +3248,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3253,7 +3263,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 740 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3270,7 +3280,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3285,7 +3295,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3302,7 +3312,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3317,7 +3327,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3334,7 +3344,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3349,7 +3359,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3366,7 +3376,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3381,7 +3391,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3398,7 +3408,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3413,7 +3423,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 870</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3430,7 +3440,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3445,7 +3455,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 490 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3462,7 +3472,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3477,7 +3487,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2530</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3494,7 +3504,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3509,7 +3519,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 1440 ≠ в нашем файле 2530</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3526,7 +3536,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3541,7 +3551,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3558,7 +3568,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3573,7 +3583,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3590,7 +3600,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3605,7 +3615,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1720</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3622,7 +3632,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3637,7 +3647,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 2000</t>
+          <t>на Авито 725 ≠ в нашем файле 1720</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3654,7 +3664,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3669,7 +3679,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>на Авито 1240 ≠ в нашем файле 2000</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3686,7 +3696,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3701,7 +3711,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3718,7 +3728,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3733,7 +3743,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3750,7 +3760,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3765,7 +3775,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 1130</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3782,7 +3792,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3797,7 +3807,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 645 ≠ в нашем файле 1130</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3814,7 +3824,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3829,7 +3839,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3846,7 +3856,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3861,7 +3871,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1130</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3878,7 +3888,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3893,7 +3903,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 745 ≠ в нашем файле 1130</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3910,7 +3920,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3925,7 +3935,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3942,7 +3952,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3957,7 +3967,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3974,7 +3984,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3984,17 +3994,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4016,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4021,7 +4031,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4038,7 +4048,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4048,17 +4058,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4080,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4085,7 +4095,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4102,7 +4112,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4117,7 +4127,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4134,7 +4144,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4149,7 +4159,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4166,7 +4176,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4181,7 +4191,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4198,7 +4208,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4230,7 +4240,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4245,7 +4255,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4262,7 +4272,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4277,7 +4287,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4294,7 +4304,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4309,7 +4319,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4326,7 +4336,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4341,7 +4351,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4358,7 +4368,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4373,7 +4383,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4390,7 +4400,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4405,7 +4415,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4422,7 +4432,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4437,7 +4447,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4454,7 +4464,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4469,7 +4479,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4486,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4501,7 +4511,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4518,7 +4528,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4533,7 +4543,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4550,7 +4560,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4565,7 +4575,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4582,7 +4592,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4614,7 +4624,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4629,7 +4639,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4646,7 +4656,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4678,7 +4688,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4693,7 +4703,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4710,7 +4720,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4742,7 +4752,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4757,7 +4767,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4774,7 +4784,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4789,7 +4799,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4806,7 +4816,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4821,7 +4831,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4838,7 +4848,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4853,7 +4863,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4870,7 +4880,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4885,7 +4895,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4902,7 +4912,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4917,7 +4927,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4934,7 +4944,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4949,7 +4959,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4966,7 +4976,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4981,7 +4991,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4998,7 +5008,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5013,7 +5023,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5030,7 +5040,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5045,7 +5055,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5062,7 +5072,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5077,7 +5087,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5094,7 +5104,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5126,7 +5136,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5141,7 +5151,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5158,7 +5168,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5173,7 +5183,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5190,7 +5200,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5205,7 +5215,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5222,7 +5232,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5237,7 +5247,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5254,7 +5264,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5269,7 +5279,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5286,7 +5296,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5301,7 +5311,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5318,7 +5328,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5333,7 +5343,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5350,7 +5360,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5365,7 +5375,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5382,7 +5392,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5397,7 +5407,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5414,7 +5424,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5429,7 +5439,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5446,7 +5456,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5461,7 +5471,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5478,7 +5488,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5510,7 +5520,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5542,7 +5552,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5574,7 +5584,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5589,7 +5599,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5606,7 +5616,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5621,7 +5631,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5638,7 +5648,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5653,7 +5663,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5670,7 +5680,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5685,7 +5695,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5702,7 +5712,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5717,7 +5727,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5734,7 +5744,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5749,7 +5759,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5766,7 +5776,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5781,7 +5791,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5798,7 +5808,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5808,17 +5818,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5840,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5845,7 +5855,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5862,7 +5872,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5877,7 +5887,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5894,7 +5904,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5909,7 +5919,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5926,7 +5936,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5941,7 +5951,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5958,7 +5968,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5973,7 +5983,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5990,7 +6000,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6005,7 +6015,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6022,7 +6032,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6037,7 +6047,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6054,7 +6064,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6069,7 +6079,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6086,7 +6096,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6101,7 +6111,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6118,7 +6128,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6133,7 +6143,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6150,7 +6160,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6165,7 +6175,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6182,7 +6192,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6197,7 +6207,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6214,7 +6224,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6229,7 +6239,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6246,7 +6256,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6261,7 +6271,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6278,7 +6288,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6293,7 +6303,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6310,7 +6320,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6325,7 +6335,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6342,7 +6352,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6357,7 +6367,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6374,7 +6384,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6389,7 +6399,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6406,7 +6416,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6421,7 +6431,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6438,7 +6448,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6453,7 +6463,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6470,7 +6480,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6485,7 +6495,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6502,7 +6512,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6517,7 +6527,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6534,7 +6544,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6549,7 +6559,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6566,7 +6576,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6581,7 +6591,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6598,7 +6608,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6613,7 +6623,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6630,7 +6640,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6645,7 +6655,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6662,7 +6672,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6677,7 +6687,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6694,7 +6704,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6709,7 +6719,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6726,7 +6736,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6741,7 +6751,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6758,7 +6768,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6773,7 +6783,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6790,7 +6800,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6805,7 +6815,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6837,7 +6847,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6854,7 +6864,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6869,7 +6879,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6886,7 +6896,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6901,7 +6911,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6918,7 +6928,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6933,7 +6943,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -6950,7 +6960,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6965,7 +6975,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -6982,7 +6992,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6997,7 +7007,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7014,7 +7024,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7029,7 +7039,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7046,7 +7056,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7061,7 +7071,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7078,7 +7088,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7093,7 +7103,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7110,7 +7120,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7125,7 +7135,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7142,7 +7152,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7157,7 +7167,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7174,7 +7184,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7189,7 +7199,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7206,7 +7216,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7221,7 +7231,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7238,7 +7248,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7253,7 +7263,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7270,7 +7280,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7285,7 +7295,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7302,7 +7312,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7317,7 +7327,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>id 4125224328 статус active</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7334,27 +7344,27 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 3965227267 статус rejected</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7376,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>0am325025Y</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7398,7 +7408,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>0am325025e</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7430,7 +7440,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7440,17 +7450,17 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -7462,59 +7472,59 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
           <t>jf015</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C212" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>нет в мастере</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7541,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -7558,12 +7568,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -7573,7 +7583,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7590,12 +7600,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -7605,7 +7615,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7622,27 +7632,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Авито/сайт</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>цена не равна правилу</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>оставить, если это сознательная цена</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7654,27 +7664,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7696,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -7701,7 +7711,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie»</t>
+          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -7718,7 +7728,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0BH325183B</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -7733,7 +7743,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie,»</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -7750,7 +7760,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7765,7 +7775,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -7782,7 +7792,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -7797,7 +7807,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -7814,7 +7824,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -7829,7 +7839,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -7846,7 +7856,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -7861,7 +7871,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -7878,7 +7888,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7893,7 +7903,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -7910,7 +7920,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7925,7 +7935,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -7942,7 +7952,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7957,7 +7967,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
+          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -7974,7 +7984,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7989,7 +7999,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
+          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8006,7 +8016,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>31705-1XF1A</t>
+          <t>31705-1XF0C</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -8021,7 +8031,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
+          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8038,7 +8048,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -8053,7 +8063,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8070,7 +8080,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>31705-X428B</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -8085,7 +8095,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
+          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8102,7 +8112,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -8117,7 +8127,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
+          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -8134,7 +8144,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -8149,7 +8159,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
+          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -8166,7 +8176,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -8181,7 +8191,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8198,32 +8208,64 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
+          <t>EA888</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>название</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
           <t>Ea888gen3</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>название</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F235" t="inlineStr">
         <is>
           <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F234"/>
+  <autoFilter ref="A1:F235"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8934,7 +8976,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie, комплект 4 шт (1 половинка)</t>
         </is>
       </c>
       <c r="C17" t="n">

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$225</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26 / 185 / 23</t>
+          <t>32 / 185 / 7</t>
         </is>
       </c>
     </row>
@@ -555,41 +555,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Маркет: название</t>
+          <t>Авито: ошибка автозагрузки</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Авито: ошибка автозагрузки</t>
+          <t>Ozon: лишний</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ozon: лишний</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>Ozon: цена</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -625,11 +625,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ozon: цена</t>
+          <t>Маркет: название</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ozon 2479 ≠ мастер 2860</t>
+          <t>Ozon 1550 ≠ мастер 879</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -816,27 +816,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>Ozon 4900 ≠ мастер 3479</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
         </is>
       </c>
     </row>
@@ -848,27 +848,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Ozon 4150 ≠ мастер 2890</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
         </is>
       </c>
     </row>
@@ -880,27 +880,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Ozon 2200 ≠ мастер 1490</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
         </is>
       </c>
     </row>
@@ -912,27 +912,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>Ozon 6200 ≠ мастер 4490</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
         </is>
       </c>
     </row>
@@ -944,27 +944,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>Ozon 2479 ≠ мастер 2860</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
         </is>
       </c>
     </row>
@@ -976,27 +976,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>Ozon 5310 ≠ мастер 2366</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1072,27 +1072,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1168,27 +1168,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1306,17 +1306,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1498,17 +1498,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1584,219 +1584,219 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig-v2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ошибка автозагрузки</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>исправить поле в шаблоне/описании</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ВАЖНО</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>salniki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>ошибка автозагрузки</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0AM325025B</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>остаток</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Ozon 13 ≠ мастер 12</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>push-stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>0AM325587E</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>остаток</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Ozon 14 ≠ мастер 13</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>push-stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>0BH325</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>TEST001</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>korpus-filtra-0bh325159</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>остаток</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Ozon 50 ≠ мастер 0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>push-stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>лишний</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1818,17 +1818,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 13 ≠ мастер 12</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 14 ≠ мастер 13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>Ozon 50 ≠ мастер 0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2160,27 +2160,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>WB: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie »</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2224,27 +2224,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2256,27 +2256,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2288,27 +2288,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2320,27 +2320,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2352,27 +2352,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>WB: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie »</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>update-cards</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>на Авито 440 ≠ в нашем файле 620</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 2940 ≠ в нашем файле 4120</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2890</t>
+          <t>на Авито 940 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>02E927770AL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 59000 ≠ в нашем файле 70800</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0AM301212A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1780</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325025B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 4740 ≠ в нашем файле 6640</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>на Авито 1740 ≠ в нашем файле 2890</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>на Авито 995 ≠ в нашем файле 1780</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 4925 ≠ в нашем файле 6900</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 39400 ≠ в нашем файле 47280</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>на Авито 1740 ≠ в нашем файле 2440</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0BH325183</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0BH325183 B</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 3990 ≠ в нашем файле 5590</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 4240</t>
+          <t>на Авито 6445 ≠ в нашем файле 9020</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 34400 ≠ в нашем файле 41280</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 64400 ≠ в нашем файле 77280</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>на Авито 2440 ≠ в нашем файле 4240</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 870</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1320</t>
+          <t>на Авито 995 ≠ в нашем файле 1390</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025n</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4490 ≠ в нашем файле 6290</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 490 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 870</t>
+          <t>на Авито 740 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325025x</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2530</t>
+          <t>на Авито 39238 ≠ в нашем файле 47090</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 2245 ≠ в нашем файле 3140</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1720</t>
+          <t>на Авито 490 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 1240 ≠ в нашем файле 2000</t>
+          <t>на Авито 4440 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
+          <t>на Авито 1440 ≠ в нашем файле 2530</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
+          <t>на Авито 1440 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 1130</t>
+          <t>на Авито 4425 ≠ в нашем файле 6200</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 725 ≠ в нашем файле 1720</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 1240 ≠ в нашем файле 2000</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1130</t>
+          <t>на Авито 466 ≠ в нашем файле 650</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>на Авито 8445 ≠ в нашем файле 11820</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
+          <t>на Авито 425 ≠ в нашем файле 600</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
+          <t>на Авито 645 ≠ в нашем файле 1130</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4026,17 +4026,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>id 4444617509 статус active</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4058,17 +4058,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>id 3964915138 статус old</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
+          <t>на Авито 745 ≠ в нашем файле 1130</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 740 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
+          <t>на Авито 29450 ≠ в нашем файле 35340</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4218,17 +4218,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>id 3964915138 статус old</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
+          <t>на Авито 1925 ≠ в нашем файле 2700</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
+          <t>на Авито 1940 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>на Авито 645 ≠ в нашем файле 900</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 745 ≠ в нашем файле 1650</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>на Авито 4445 ≠ в нашем файле 6220</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
+          <t>на Авито 475 ≠ в нашем файле 670</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 3879 ≠ в нашем файле 2720</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 1445 ≠ в нашем файле 2020</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 490 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 495 ≠ в нашем файле 690</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
+          <t>на Авито 3750 ≠ в нашем файле 5250</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
+          <t>на Авито 7500 ≠ в нашем файле 5850</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
+          <t>на Авито 4250 ≠ в нашем файле 5950</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
+          <t>на Авито 4750 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-niz-dq200</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 9500 ≠ в нашем файле 6650</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-verh-dq200</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
+          <t>на Авито 620 ≠ в нашем файле 870</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
+          <t>на Авито 1995 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
+          <t>на Авито 3990 ≠ в нашем файле 2790</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
+          <t>на Авито 690 ≠ в нашем файле 970</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
+          <t>на Авито 420 ≠ в нашем файле 590</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
+          <t>на Авито 290 ≠ в нашем файле 410</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
+          <t>на Авито 925 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
+          <t>на Авито 1450 ≠ в нашем файле 2090</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
+          <t>на Авито 1425 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 2850 ≠ в нашем файле 1990</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 745 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 850 ≠ в нашем файле 1040</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 1245 ≠ в нашем файле 1740</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>на Авито 845 ≠ в нашем файле 1180</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
+          <t>на Авито 945 ≠ в нашем файле 1320</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
+          <t>на Авито 500 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
+          <t>на Авито 245 ≠ в нашем файле 340</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5850,17 +5850,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>id 4284998704 статус active</t>
+          <t>на Авито 935 ≠ в нашем файле 1310</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5882,17 +5882,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>id 4284880578 статус active</t>
+          <t>на Авито 2850 ≠ в нашем файле 3990</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5914,17 +5914,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>id 4220734432 статус active</t>
+          <t>на Авито 975 ≠ в нашем файле 1370</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>id 4125069388 статус active</t>
+          <t>на Авито 3700 ≠ в нашем файле 5180</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5978,17 +5978,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>id 4284610725 статус active</t>
+          <t>на Авито 4450 ≠ в нашем файле 6230</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6010,17 +6010,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>объявление не из фида</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>id 4285296851 статус active</t>
+          <t>на Авито 2495 ≠ в нашем файле 3490</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>закрыть, если старое/дубль</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>id 4284955885 статус active</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>id 4285324155 статус active</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Корпус фильтра DQ500 DSG7</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>id 4348814868 статус active</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Корпус фильтра DSG6 DQ250 02E</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>id 4349172359 статус active</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>id 4444968174 статус active</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>id 4124845206 статус active</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>id 4444712249 статус active</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>id 4444869727 статус rejected</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>id 4349334275 статус active</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>id 4285328953 статус active</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>id 4444524662 статус active</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>id 3965344207 статус active</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>id 4573121040 статус active</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>id 4253114863 статус active</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>id 3965207177 статус active</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>id 4125079566 статус active</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>id 3965211558 статус active</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>id 4253030337 статус active</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>id 4573102274 статус active</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>id 3965565847 статус active</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
+          <t>Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>id 4445119215 статус active</t>
+          <t>id 3965207177 статус active</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>id 4189437762 статус active</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
+          <t>Ремкомплект (прокладки) мехатроника DSG7 DQ200 0am</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>id 4220978299 статус active</t>
+          <t>id 3965211558 статус active</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>id 4125283125 статус active</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>id 4445230063 статус active</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>id 4285108577 статус active</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>id 4220729305 статус active</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Сальник толькателя мехатроника dq200 dsg7</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>id 7260608738 статус active</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>id 4445242895 статус active</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Соленоид dq200 dsg 7 bosch новый</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>id 4124730141 статус active</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>id 4284950339 статус active</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>id 3965336925 статус active</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>id 4124828843 статус old</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>id 3964990179 статус old</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>id 4125257871 статус old</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>id 4284973404 статус active</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Фильтр DQ250 DSG 6 02E305051C</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>id 4317088408 статус rejected</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Фильтр АКПП DSG 7 0BH325183B</t>
+          <t>Соленоид мехатроника DSG 7 DQ200 Bosch регулятор</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>id 4316875109 статус active</t>
+          <t>id 3965336925 статус active</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>id 4284733993 статус active</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Штоки dq200 dsg7 0am 0cw</t>
+          <t>Соленоиды dsg 7 dq200 0am дсг 7</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>id 4572853508 статус active</t>
+          <t>id 3964990179 статус old</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>id 4125224328 статус active</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>id 3965227267 статус rejected</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7376,27 +7376,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>0am325025Y</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7408,27 +7408,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>0am325025e</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7440,27 +7440,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>0b5</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>нет в мастере</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>товар есть на площадке, но в master_control его нет</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>завести в мастер или убрать с площадки</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7472,27 +7472,27 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -7504,219 +7504,219 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>id 4125224328 статус active</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Штоки мехатроника DSG7 DQ200 Штоки дсг 7</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Авито</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>объявление не из фида</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>id 3965227267 статус rejected</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>закрыть, если старое/дубль</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>0am325025Y</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>0am325025e</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>0b5</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>TEST001</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
           <t>jf015</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>Маркет</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>нет в мастере</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>завести в мастер или убрать с площадки</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Ozon</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Tilda</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>WB</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>в мастере «Dq500», на площадке «DQ500»</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>0BH325183B</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>артикул отличается регистром</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Авито/сайт</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>цена не равна правилу</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>оставить, если это сознательная цена</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>0AM325467J</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Маркет: «Сепараторная пластина под плиту мехатроника DSG7 п» ≠ мастер: «Оригинальная сепараторная пластина мехатроника VAG»</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
@@ -7728,27 +7728,27 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Маркет: «Соленоиды мехатроника DSG7 DQ200 0AM325473 0CW ком» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie,»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7792,27 +7792,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DSG 7 DQ200 | Прокладки, г» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 (гидроплита, са»</t>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7824,27 +7824,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Маркет: «Планка соленоидов DSG7 DQ200 0AM Пластик 1 шт» ≠ мастер: «Пластина соленоидов мехатроника DSG7 DQ200 0AM3254»</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
@@ -7856,27 +7856,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Маркет</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Маркет: «Прокладка электронной платы 0am 0cw dq200 dsg 7» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7888,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -7903,7 +7903,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Маркет: «Ремкомплект мехатроника DQ200 DSG7 + оригиналы пыл» ≠ мастер: «Ремкомплект мехатроника DSG7 DQ200 + оригинальные »</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Маркет: «Уплотнение резиновое электромотора гидроблока (мех» ≠ мастер: «Уплотнение электромотора гидроблока мехатроника DS»</t>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -7944,328 +7944,8 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>0cw325025h</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладка платы электронной мехатроника DSG7 DQ200» ≠ мастер: «Прокладка электронной платы мехатроника DSG7 DQ200»</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Маркет: «Пыльник штока мехатроника DQ200 DSG7 0AM Оригинал » ≠ мастер: «Оригинальный пыльник штока мехатроника DSG7 DQ200 »</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011Новое поколение (RE0F10A)» ≠ мастер: «Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 3»</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>31705-1XF1A</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок JF015E 1.6 Л. CVT (RE0F11A) для Nissan, » ≠ мастер: «Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 3»</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Маркет: «Гидроблок вариатора JF015E 1.8 Л. (RE0F11A) CVT дл» ≠ мастер: «Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX»</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Dq200dsg7</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>Маркет: «Уплотнение насоса мехатроника (гидроблока) DQ200 0» ≠ мастер: «Уплотнение насоса гидроблока мехатроника DSG7 DQ20»</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>Маркет: «Прокладки DQ200 DSG7+сальники и пыльники Оригинал » ≠ мастер: «Прокладки + сальники + пыльники мехатроника DSG7 D»</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>EA888</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Маркет: «Корпус фильтра EA888» ≠ мастер: «Алюминиевый корпус масляного фильтра EA888 Gen3 (к»</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>НИЗКО</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Ea888gen3</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Маркет</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>название</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>Маркет: «Магнит на корпус масляного фильтра EA888 Gen 3» ≠ мастер: «Обратный клапан масляного фильтра EA888 Gen3 06L11»</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F235"/>
+  <autoFilter ref="A1:F225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/audit_report.xlsx
+++ b/data/audit_report.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Матрица" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Проблемы'!$A$1:$F$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Матрица'!$A$1:$I$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32 / 185 / 7</t>
+          <t>16 / 81 / 7</t>
         </is>
       </c>
     </row>
@@ -535,107 +535,107 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Авито: цена</t>
+          <t>Авито: объявление не из фида</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Авито: объявление не из фида</t>
+          <t>Ozon: лишний</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Авито: ошибка автозагрузки</t>
+          <t>Ozon: остаток</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ozon: лишний</t>
+          <t>WB: нет на площадке</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WB: нет на площадке</t>
+          <t>Маркет: нет в мастере</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ozon: цена</t>
+          <t>Авито: ошибка автозагрузки</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Маркет: нет в мастере</t>
+          <t>Авито: нет на площадке</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Авито: нет на площадке</t>
+          <t>Ozon: цена</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ozon: остаток</t>
+          <t>Маркет: название</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Маркет: название</t>
+          <t>Tilda: лишний</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tilda: лишний</t>
+          <t>WB: название</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -645,7 +645,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WB: название</t>
+          <t>WB: лишний</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -655,7 +655,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WB: лишний</t>
+          <t>Авито: цена</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F225"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ozon 1550 ≠ мастер 879</t>
+          <t>Ozon 2479 ≠ мастер 2860</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ozon 4900 ≠ мастер 3479</t>
+          <t>Ozon 5310 ≠ мастер 2366</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -848,27 +848,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ozon 4150 ≠ мастер 2890</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -880,27 +880,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ozon 2200 ≠ мастер 1490</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -912,27 +912,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ozon 6200 ≠ мастер 4490</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -944,27 +944,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ozon 2479 ≠ мастер 2860</t>
+          <t>остаток 45</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -976,27 +976,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет на площадке</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ozon 5310 ≠ мастер 2366</t>
+          <t>остаток 31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>update-cards (push-photos/push-ozon-cards) или проверьте ручную акцию</t>
+          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>остаток 100</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 43</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>остаток 50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>остаток 45</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:  — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;  — перечёркнуто</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>остаток 31</t>
+          <t>остаток 13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>остаток 100</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>остаток 43</t>
+          <t>остаток 9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
         </is>
       </c>
     </row>
@@ -1232,27 +1232,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>ошибка автозагрузки</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>остаток 50</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:  — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;  — перечёркнуто</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>создать карточку WB: команда wb-create-missing-dryrun, затем wb-create-missing (tools)</t>
+          <t>исправить поле в шаблоне/описании</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Неверный параметр «Состояние»:  Сейчас информация в параметрах объявления и в описании отличается — это путает покупателей и снижает доверие к объявлению.  Отр</t>
+          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:  — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;  — перечёркнуто</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1289,514 +1289,514 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>Ozon 15 ≠ мастер 13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>Ozon 9 ≠ мастер 7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0BH325</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>Ozon 16 ≠ мастер 17</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>остаток 13</t>
+          <t>Ozon 35 ≠ мастер 34</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Ozon 160 ≠ мастер 161</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ea888gen3</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>нет на площадке</t>
+          <t>остаток</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>остаток 9</t>
+          <t>Ozon 16 ≠ мастер 17</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>нет объявления на Авито — смотрите ошибки автозагрузки; для двигателя нужен другой шаблон категории</t>
+          <t>push-stock</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>остаток</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ozon 50 ≠ мастер 0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>push-stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>kryshka-mehatronika-dq200</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>остаток</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ozon 19 ≠ мастер 20</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>push-stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>plita-filtr</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-orig</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>plita-filtr-salniki-orig</t>
-        </is>
-      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>plita-filtr-orig</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>остаток</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ozon 16 ≠ мастер 17</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>push-stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>plita-filtr-v2</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>лишний</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>СРЕДНЕ</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>ошибка автозагрузки</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>исправить поле в шаблоне/описании</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ВАЖНО</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Ozon</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ошибка автозагрузки</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Объявление отклонено и не будет опубликовано до устранения причин отклонения.  Устраните нарушения в описании объявления в своем XML-файле.  Фото выделено:  Поменяйте или удалите первое фото — на нём не должно быть:   — слов «распродажа», «скидка», «акция», «дёшево», «срочно» и т. п.;   — перечёркну</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>исправить поле в шаблоне/описании</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1818,17 +1818,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ozon 13 ≠ мастер 12</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ozon 14 ≠ мастер 13</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0BH325</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>остаток</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ozon 50 ≠ мастер 0</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>push-stock</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Tilda</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2032,27 +2032,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>WB: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie »</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>update-cards</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>TESTWB001</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>WB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>цена</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>на Авито 890 ≠ в нашем файле 700</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
         </is>
       </c>
     </row>
@@ -2128,27 +2128,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4444617509 статус active</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2160,27 +2160,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>Болты мехатроника dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4284998704 статус active</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2192,27 +2192,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>Гидроаккумулятор DSG7 DQ200 0AM 0CW Оригинал VAG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4284880578 статус active</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2224,27 +2224,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 8324486269 статус old</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2256,27 +2256,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 8387447350 статус old</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2288,27 +2288,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
+          <t>Гидроплита dsg 7 dq200 усиленная ремкомплект dsg7</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ozon</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4220734432 статус active</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2320,27 +2320,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TEST001</t>
+          <t>Гильза мехатроника DSG 7 DQ200 0AM 0CW новая</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tilda</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4125069388 статус active</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2352,27 +2352,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>Заглушка коробки DSG7 DQ200 0AM 0CW 52м</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>название</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>WB: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie» ≠ мастер: «Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie »</t>
+          <t>id 4284610725 статус active</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>update-cards</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TESTWB001</t>
+          <t>Кольцо гидроаккумулятора dq200 dsg 7 0am 0cw</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>Авито</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>лишний</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
+          <t>id 4285296851 статус active</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>убрать с площадки (remove-product) или поставить «да»</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01X301127C</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2426,17 +2426,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>на Авито 440 ≠ в нашем файле 620</t>
+          <t>id 8302806177 статус old</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2458,17 +2458,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>на Авито 2940 ≠ в нашем файле 4120</t>
+          <t>id 8389544247 статус rejected</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>Корпус фильтра DQ250 DSG 6 02E305045</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>на Авито 940 ≠ в нашем файле 1320</t>
+          <t>id 4284955885 статус active</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02E927770AL</t>
+          <t>Корпус фильтра DQ500 DSG 7 0BH325183</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2522,17 +2522,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>на Авито 59000 ≠ в нашем файле 70800</t>
+          <t>id 4285324155 статус active</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>Корпус фильтра DQ500 DSG7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2554,17 +2554,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>id 4348814868 статус active</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0AM301212A</t>
+          <t>Корпус фильтра DSG6 DQ250 02E</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>id 4349172359 статус active</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
+          <t>Крышка поддон мехатроника+прокладка DSG 7 DQ200</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>на Авито 4740 ≠ в нашем файле 6640</t>
+          <t>id 4444968174 статус active</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0AM325120A</t>
+          <t>Манжеты сальники мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4124845206 статус active</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>Масляный фильтр АКПП DSG 7 DQ500</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2682,17 +2682,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2890</t>
+          <t>id 4444712249 статус active</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>Новая фильтр сетка на соленоид АКПП DSG7 0B5 DL501</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2714,17 +2714,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
+          <t>id 4444869727 статус rejected</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>Плита DQ200 0am 0cw (усиленная гидроплита DSG 7)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2746,17 +2746,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>id 4349334275 статус active</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>Подшипник вилки DQ200 DSG-7 0AM 0CW 6/R</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2778,17 +2778,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1780</t>
+          <t>id 4285328953 статус active</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>Поршень вилки мехатроника DSG7 DQ200 0AM/0CW</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2810,17 +2810,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>id 4444524662 статус active</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>Прокладка DQ200 DSG 7 Прокладка крышки мехатроника</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2842,17 +2842,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>на Авито 4925 ≠ в нашем файле 6900</t>
+          <t>id 3965344207 статус active</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>Прокладки dq200 ремкомплект dsg 7 0am</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2874,17 +2874,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>на Авито 39400 ≠ в нашем файле 47280</t>
+          <t>id 4573121040 статус active</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>Прокладки dsg 7 сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>на Авито 1740 ≠ в нашем файле 2440</t>
+          <t>id 4253114863 статус active</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0BH325183</t>
+          <t>Пыльник штоков мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2938,17 +2938,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>id 4125079566 статус active</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>Ремкомплект dq200 dsg7 0am гидроплита прокладки</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>на Авито 3990 ≠ в нашем файле 5590</t>
+          <t>id 4253030337 статус active</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>Ремкомплект dsg 7 dq200 усиленная плита прокладки</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3002,17 +3002,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>на Авито 6445 ≠ в нашем файле 9020</t>
+          <t>id 4573102274 статус active</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3034,17 +3034,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
+          <t>id 3965565847 статус active</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>Ремкомплект мехатроника dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>id 4445119215 статус active</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>Ремкомплект мехатроника dsg 7 dq200 плита фильтр</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3098,17 +3098,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>на Авито 34400 ≠ в нашем файле 41280</t>
+          <t>id 4189437762 статус active</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>Ремкомплект мехатроника dsg7 dq200 0am</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>на Авито 64400 ≠ в нашем файле 77280</t>
+          <t>id 4220978299 статус active</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>Ремкомплект прокладки мехатроника DSG 7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>id 4125283125 статус active</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>Ремкомплект штока DQ200 DSG7 0AM 0CW шток + втулка</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3194,17 +3194,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>на Авито 2440 ≠ в нашем файле 4240</t>
+          <t>id 4445230063 статус active</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3226,17 +3226,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
+          <t>id 4285108577 статус active</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>Ремкомплект штока мехатроника DSG 7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>на Авито 995 ≠ в нашем файле 1390</t>
+          <t>id 4220729305 статус active</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>Сальник толькателя мехатроника dq200 dsg7</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3290,17 +3290,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>id 7260608738 статус active</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>id 4445242895 статус active</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>Соленоид dq200 dsg 7 bosch новый</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3354,17 +3354,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>id 4124730141 статус active</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0am325025n</t>
+          <t>Соленоид dsg 7 dq200 0am 0cw регулятор давления</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>на Авито 4490 ≠ в нашем файле 6290</t>
+          <t>id 4284950339 статус active</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>Соленоиды dsg 7 dq200 0am 0cw</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3418,17 +3418,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 870</t>
+          <t>id 4124828843 статус old</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1320</t>
+          <t>id 8425207775 статус old</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>Соленоиды АКПП 6t30 6t40 6t45 6t50</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>id 4125257871 статус old</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0am325025x</t>
+          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>на Авито 39238 ≠ в нашем файле 47090</t>
+          <t>id 8314430321 статус rejected</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3546,17 +3546,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>на Авито 2245 ≠ в нашем файле 3140</t>
+          <t>id 4284973404 статус active</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>Фильтр DQ250 DSG 6 02E305051C</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3578,17 +3578,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>id 4317088408 статус rejected</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>Фильтр АКПП DSG 7 0BH325183B</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3610,17 +3610,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
+          <t>id 4316875109 статус active</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>Фильтр-сетка соленоид DL501 0B5 DSG7 N436/N440 1шт</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3642,17 +3642,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 870</t>
+          <t>id 4284733993 статус active</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>Штоки dq200 dsg7 0am 0cw</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3674,17 +3674,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>на Авито 4440 ≠ в нашем файле 6220</t>
+          <t>id 4572853508 статус active</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>Штоки dsg7 dq200 (шток дсг 7)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>объявление не из фида</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2530</t>
+          <t>id 4125224328 статус active</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>закрыть, если старое/дубль</t>
         </is>
       </c>
     </row>
@@ -3728,27 +3728,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325025Y</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -3760,27 +3760,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325025e</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>на Авито 1440 ≠ в нашем файле 2020</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -3792,27 +3792,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0b5</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>нет в мастере</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>на Авито 4425 ≠ в нашем файле 6200</t>
+          <t>товар есть на площадке, но в master_control его нет</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>завести в мастер или убрать с площадки</t>
         </is>
       </c>
     </row>
@@ -3824,27 +3824,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>TEST001</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>лишний</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>на Авито 725 ≠ в нашем файле 1720</t>
+          <t>в мастере для этой площадки стоит «нет», но товар на ней есть</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>убрать с площадки (remove-product) или поставить «да»</t>
         </is>
       </c>
     </row>
@@ -3856,4096 +3856,256 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>jf015</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>Маркет</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>нет в мастере</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>товар есть на площадке, но в master_control его нет</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>завести в мастер или убрать с площадки</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ozon</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tilda</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Dq500</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>WB</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>артикул отличается регистром</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>в мастере «Dq500», на площадке «DQ500»</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0BH325183B</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
           <t>Авито</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>на Авито 1240 ≠ в нашем файле 2000</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>0cw0am</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>на Авито 466 ≠ в нашем файле 650</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>0cw0am325025</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>на Авито 8445 ≠ в нашем файле 11820</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>0cw0amdsgdq200</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>на Авито 425 ≠ в нашем файле 600</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>0cw325025h</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>артикул отличается регистром</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>на Авито 645 ≠ в нашем файле 1130</t>
+          <t>в мастере «0BH325183B», на площадке «0BH325183 B»</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>привести к одному написанию (или оставить, если так заведено исторически)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Авито/сайт</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>цена не равна правилу</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
+          <t>Авито/сайт 5850, по правилу (70% от маркетплейса) 5250</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>оставить, если это сознательная цена</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0BH325183B</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
+          <t>Маркет: «Корпус фильтра DQ500 DSG7 0BH325183B» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
+          <t>поправить в кабинете Маркета (названия через API не синхронизируются)</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>НИЗКО</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>31705-1XF1A</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Авито</t>
+          <t>Маркет</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>цена</t>
+          <t>название</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>на Авито 745 ≠ в нашем файле 1130</t>
+          <t>Маркет: «Гидроблок вариатора JF011E Старое поколение RE0F10» ≠ мастер: «»</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>123014‑AF</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>на Авито 740 ≠ в нашем файле 1040</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>на Авито 29450 ≠ в нашем файле 35340</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>55565480</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>на Авито 890 ≠ в нашем файле 700</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Bмасляный фильтр АКПП DSG6 DQ250 02E305051C</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>id 4444617509 статус active</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Cоленоиды 6T30 6T40 6T45 6T50</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>объявление не из фида</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>id 3964915138 статус old</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>закрыть, если старое/дубль</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>DQ500</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>на Авито 1925 ≠ в нашем файле 2700</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Dq200dsg7</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>на Авито 1940 ≠ в нашем файле 2720</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>WHT001922</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>filtr-dsg7-dq200</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>filtr-dsg7-dq500</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>на Авито 645 ≠ в нашем файле 900</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>filtr-setka-0b5-orig</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>на Авито 745 ≠ в нашем файле 1650</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>gidroakkumulyator-orig</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>на Авито 4445 ≠ в нашем файле 6220</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>klipsy-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>на Авито 475 ≠ в нашем файле 670</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>korpus-filtra-0bh325159</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>на Авито 3879 ≠ в нашем файле 2720</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>kryshka-mehatronika-dq200</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>planka-solenoid-2sht</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>на Авито 1445 ≠ в нашем файле 2020</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>plastina-solenoid-dq200</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>plastiny-solenoid-dq200-2sht</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>на Авито 490 ≠ в нашем файле 690</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>plastiny-solenoid-orig</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>на Авито 495 ≠ в нашем файле 690</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>plita-filtr-orig</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>на Авито 3750 ≠ в нашем файле 5250</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-orig</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>plita-filtr-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>на Авито 7500 ≠ в нашем файле 5850</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>на Авито 4250 ≠ в нашем файле 5950</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>на Авито 4750 ≠ в нашем файле 6650</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>на Авито 9500 ≠ в нашем файле 6650</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>на Авито 620 ≠ в нашем файле 870</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>на Авито 1995 ≠ в нашем файле 2790</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>на Авито 3990 ≠ в нашем файле 2790</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>prokladka-kryshki-dq200</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>на Авито 690 ≠ в нашем файле 970</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>prokladka-vtulki-dq200</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>на Авито 420 ≠ в нашем файле 590</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>prokladka-vtulki-niz-dq200</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>prokladka-vtulki-verh-dq200</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>на Авито 290 ≠ в нашем файле 410</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>на Авито 925 ≠ в нашем файле 2090</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig-v2</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>на Авито 1450 ≠ в нашем файле 2090</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>remkomplekt-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>на Авито 1425 ≠ в нашем файле 1990</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>на Авито 2850 ≠ в нашем файле 1990</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>на Авито 745 ≠ в нашем файле 1040</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>на Авито 850 ≠ в нашем файле 1040</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>salnik-tolkatelya-alum</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>на Авито 1245 ≠ в нашем файле 1740</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>на Авито 845 ≠ в нашем файле 1180</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>на Авито 945 ≠ в нашем файле 1320</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>salniki-tolkatelya-4sht</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>salnikprivod-l</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>salnikprivod-r</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>на Авито 500 ≠ в нашем файле 700</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>separatornaya-plastina-dq200</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>на Авито 245 ≠ в нашем файле 340</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>separatornaya-plastiny-solenoid-dq200</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>на Авито 935 ≠ в нашем файле 1310</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>solenoid-02e-0b5-bolshoy</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>на Авито 2850 ≠ в нашем файле 3990</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>stalnaya-vstavka-plity</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>на Авито 975 ≠ в нашем файле 1370</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>tolkateli-4-salniki-4</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>на Авито 3700 ≠ в нашем файле 5180</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>на Авито 4450 ≠ в нашем файле 6230</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>vtulki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Авито</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>цена</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>на Авито 2495 ≠ в нашем файле 3490</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>дождаться следующей автозагрузки / проверить её отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>СРЕДНЕ</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Болты мехатроника dq20